--- a/data/Inventario_Manuales.xlsx
+++ b/data/Inventario_Manuales.xlsx
@@ -12,6 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Morley" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifier" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kidde" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aritech" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edwards" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otros" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -642,17 +645,110 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Portal firesecurityproducts (paneles Control · ES+EN)</t>
-        </is>
-      </c>
-    </row>
+          <t>Portal firesecurityproducts — paneles Control (s52) + base instalada TRATEIN (Excellence/ModuLaser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Aritech</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" t="n">
+        <v>33</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Portal firesecurityproducts — base instalada TRATEIN (paneles 2X-A, detección serie 2000, módulos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Edwards</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Portal firesecurityproducts — base instalada TRATEIN (ModuLaser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Portal firesecurityproducts — base instalada TRATEIN (genéricos sin marca: tubería, cable, accesorios)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -34169,7 +34265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -34455,12 +34551,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2X-AF1-S</t>
+          <t>KE-DM3010R-KIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -34475,17 +34571,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2x-af1-s-161721-es.pdf</t>
+          <t>03-0210-501-4300-06_r006_excellence_series_addressable_mcp_installation_sheet_ml.pdf</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>890</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2X-AF2-FB</t>
+          <t>2X-AF1-S</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -34505,17 +34601,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2x-af2-fb-161721-es.pdf</t>
+          <t>2x-af1-s-161721-es.pdf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1101</v>
+        <v>890</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2X-AF2-FB-S</t>
+          <t>2X-AF2-FB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -34535,17 +34631,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2x-af2-fb-s-161721-es.pdf</t>
+          <t>2x-af2-fb-161721-es.pdf</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>952</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2X-AF2-SCFB</t>
+          <t>2X-AF2-FB-S</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -34565,17 +34661,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2x-af2-scfb-161721-es.pdf</t>
+          <t>2x-af2-fb-s-161721-es.pdf</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1090</v>
+        <v>952</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2X-AF2-SCFB-S</t>
+          <t>2X-AF2-SCFB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -34595,17 +34691,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2x-af2-scfb-s-161721-es.pdf</t>
+          <t>2x-af2-scfb-161721-es.pdf</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>903</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2X-AT-F2</t>
+          <t>2X-AF2-SCFB-S</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -34625,17 +34721,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2x-at-f2-161721-es.pdf</t>
+          <t>2x-af2-scfb-s-161721-es.pdf</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>497</v>
+        <v>903</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2X-AT-F2-FB</t>
+          <t>2X-AT-F2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -34655,17 +34751,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2x-at-f2-fb-161721-es.pdf</t>
+          <t>2x-at-f2-161721-es.pdf</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>473</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2X-AT-F2-FB-P</t>
+          <t>2X-AT-F2-FB</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -34685,17 +34781,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2x-at-f2-fb-p-161721-es.pdf</t>
+          <t>2x-at-f2-fb-161721-es.pdf</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2X-AT-F2-FB-S</t>
+          <t>2X-AT-F2-FB-P</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -34715,17 +34811,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2x-at-f2-fb-s-161721-es.pdf</t>
+          <t>2x-at-f2-fb-p-161721-es.pdf</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>339</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2X-AT-F2-P</t>
+          <t>2X-AT-F2-FB-S</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -34745,17 +34841,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2x-at-f2-p-161721-es.pdf</t>
+          <t>2x-at-f2-fb-s-161721-es.pdf</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>473</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2X-AT-F2-S</t>
+          <t>2X-AT-F2-P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -34775,27 +34871,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2x-at-f2-s-161721-es.pdf</t>
+          <t>2x-at-f2-p-161721-es.pdf</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>523</v>
+        <v>473</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2X-A Táctil</t>
+          <t>2X-AT-F2-S</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Manual técnico</t>
+          <t>Datasheet</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -34805,17 +34901,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3103267-en_r001_2x-a_series_kuwait_marketplace_manual.pdf</t>
+          <t>2x-at-f2-s-161721-es.pdf</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>355</v>
+        <v>523</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>KE-DP3020W</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -34835,22 +34931,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>bcn-3100017-es_r002_nc_series_fire_alarm_control_panel_installation_manual.pdf</t>
+          <t>3102984-ml_r003_excellence_series_intelligent_addressable_dual_optical_detector_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3723</v>
+        <v>716</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>KE-DT3001W-HAB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Manual usuario</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -34865,22 +34961,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>bcn-3100018-es_r002_nc_series_fire_alarm_control_panel_operation_manual.pdf</t>
+          <t>3102986-ml_r002_excellence_series_intelligent_addressable_class_a-b_heat_detector_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>767</v>
+        <v>724</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>KE-DB3010W</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -34895,22 +34991,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>bcn-3100019-es_r002_nc_series_fire_alarm_control_panel_quick_installation_guide.pdf</t>
+          <t>3102987-ml_r003_excellence_series_standard_mounting_base_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>323</v>
+        <v>659</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>KE-DBA-AUXW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -34925,27 +35021,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>bcn-3100020-es_r002_nc_series_fire_alarm_control_panel_quick_operation_guide.pdf</t>
+          <t>3103013-ml_r002_ke-dba-auxw_deep_accessory_for_standard_mounting_base_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>222</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2X-A Táctil</t>
+          <t>KE-IO3101</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manual técnico</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -34955,27 +35051,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>bcn-3100035-en_r006_2x-a_series_addressable_control_panel_compatibility_list_0.pdf</t>
+          <t>3103062-ml_r003_excellence_series_addressable_single_output_module_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>215</v>
+        <v>636</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2X-A Táctil</t>
+          <t>KE-IO3122</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Manual técnico</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -34985,22 +35081,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>bcn-3100036-en_r002_2x-a_and_zp2-a_series_addressable_control_panel_compatibility_list_900_series_protocol.pdf</t>
+          <t>3103063-ml_r003_excellence_series_addressable_two-four_input-output_module_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>193</v>
+        <v>839</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NC-PF2</t>
+          <t>KE-AS3115R-WM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -35015,22 +35111,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>nc-pf2-161721-es.pdf</t>
+          <t>3103072-ml_r004_excellence_series_intelligent_addressable_indoor_notification_device_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>497</v>
+        <v>3036</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NC-PF4</t>
+          <t>9-30781-KID-EN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -35045,22 +35141,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>nc-pf4-161721-es.pdf</t>
+          <t>3103092-es_r003_modulaser_en_54-20_installation_manual_kidde_0.pdf</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>622</v>
+        <v>6029</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NC-PF4-SC</t>
+          <t>KE-AS3115R-WMIP</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -35075,27 +35171,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>nc-pf4-sc-161721-es.pdf</t>
+          <t>3103198-ml_r002_excellence_series_intelligent_addressable_outdoor_notification_device_installation_sheet.pdf</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>628</v>
+        <v>3366</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NC-PF8</t>
+          <t>2X-A Táctil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Datasheet</t>
+          <t>Manual técnico</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -35105,19 +35201,1723 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>nc-pf8-161721-es.pdf</t>
+          <t>3103267-en_r001_2x-a_series_kuwait_marketplace_manual.pdf</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>560</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>9-30781-KID-EN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>9-30781-kid-en-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>9-30783-KID-EN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>9-30783-kid-en-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>bcn-3100017-es_r002_nc_series_fire_alarm_control_panel_installation_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>bcn-3100018-es_r002_nc_series_fire_alarm_control_panel_operation_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>bcn-3100019-es_r002_nc_series_fire_alarm_control_panel_quick_installation_guide.pdf</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bcn-3100020-es_r002_nc_series_fire_alarm_control_panel_quick_operation_guide.pdf</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bcn-3100035-en_r006_2x-a_series_addressable_control_panel_compatibility_list_0.pdf</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bcn-3100036-en_r002_2x-a_and_zp2-a_series_addressable_control_panel_compatibility_list_900_series_protocol.pdf</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ke-as3115r-wm-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WMIP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ke-as3115r-wmip-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KE-DB3010W</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ke-db3010w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>KE-DBA-AUXW</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ke-dba-auxw-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KE-DM3010R</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ke-dm3010r-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KE-DM3010R-KIT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ke-dm3010r-kit-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KE-DP3020W</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ke-dp3020w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KE-DP3120W</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ke-dp3120w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KE-DT3001W-HAB</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ke-dt3001w-hab-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KE-IO3101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ke-io3101-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KE-IO3122</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ke-io3122-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KE-IO3144</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ke-io3144-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NC-PF2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>nc-pf2-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NC-PF4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>nc-pf4-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NC-PF4-SC</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>nc-pf4-sc-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NC-PF8</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>nc-pf8-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>NC-PF8-SC</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>nc-pf8-sc-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>617</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Tipo documento</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Idioma</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Subcarpeta</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Tamaño (KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2X-LB</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00-3218-501-0000-07_r007_2x-lb_installation_sheet_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00-3280-501-4003-05_r005_2x-a_series_installation_manual_en_0.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4810</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2X-AF2-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>00-3280-501-4009-05_r005_2x-a_series_installation_manual_es.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2X-AF2-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00-3280-505-4009-04_r004_2x-a_series_operation_manual_es.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>00-3280-507-4003-03_r003_2x-a_series_quick_installation_guide_en.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2X-AF2-09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00-3280-507-4009-03_r003_2x-a_series_quick_installation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2X-AF2-09</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00-3280-508-4009-03_r003_2x-a_series_quick_operation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00-3280-508-4109-06_r006_2x-at_series_quick_start_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00-3280-508-4209-02_r002_2x-at_series_quick_operation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2X-A-LB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00-3301-501-4000-04_r004_2x-a-lb_loop_board_installation_sheet_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2010-2A-PAK-HPL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00-3301-501-4100-04_r004_2010-2a-pak-hpl_registration_guide_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FD2705R</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0044-055-02_-_aritech_ra_-_fd2705-10r_addendum_-_en_de.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>IU2055NC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10-5106-501-55nc-05_r005_iu2055nc_installation_sheet_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AS2364</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>18-187110-10.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2010-2-PAK-RMSDK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2010-2-pak-rmsdk-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2010-2A-PAK-HPL</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2010-2a-pak-hpl-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FD2705R</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>22318.18.08_-_aritech_ra_-_fd2705-10r_english_std_reflective_user_guide_-_en.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2X-A-LB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2x-a-lb-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2X-AF2-09</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2x-af2-09-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2x-at-f2-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2X-LB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2x-lb-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3103267-en_r001_2x-a_series_kuwait_marketplace_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ASW2367</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>aritech_ins570-8_combined.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AS2363</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>as2363-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AS2364</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>as2364-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASW2366</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>asw2366-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASW2367</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>asw2367-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2010-2-PAK-RMSDK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>bcn-3100032-ml_r002_2010-2-pak-rmsdk_registration_guide.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>bcn-3100035-en_r006_2x-a_series_addressable_control_panel_compatibility_list_0.pdf</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>bcn-3100036-en_r002_2x-a_and_zp2-a_series_addressable_control_panel_compatibility_list_900_series_protocol.pdf</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>FD2705R</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Datasheet</t>
@@ -35135,11 +36935,749 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>nc-pf8-sc-161721-es.pdf</t>
+          <t>fd2705r-62536-es.pdf</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>617</v>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FD2710R</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>fd2710r-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IU2055NC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>iu2055nc-62536-es.pdf</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1069</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Tipo documento</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Idioma</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Subcarpeta</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Tamaño (KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FHSD8310</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>04-4001-501-2009-12_r012_modulaser_en_54-20_installation_manual_es_edwards_0.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6021</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FHSD8310</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>fhsd8310-63296-es.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FHSD8330</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fhsd8330-63296-es.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>462</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Tipo documento</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Idioma</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Subcarpeta</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Tamaño (KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>N-MC-BB-G</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>03-0210-501-4301-02_r002_n-mc_series_mcp_backbox_installation_sheet_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NC-MC-0-G</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>03-0211-501-3000-05_r005_nc_series_conventional_mcp_installation_sheet_ml_0.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9-30441</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>04-4001-501-1700-06_r006_aritech_apic_installation_sheet_ml_0.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD68N-0100</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20-8501-509-dl03-04_alarmline_ii_digital_lhd_cable_technical_manual_en.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>9-10900</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9-10900-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>9-10906</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9-10906-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9-10908</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9-10908-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>9-10909</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9-10909-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9-10927</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9-10927-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>9-10954-100</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9-10954-100-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9-30441</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>9-30441-62576-es.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AD68N-0100</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ad68n-0100-1-es.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DM715</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dm715-63296-es.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>N-MC-BB-G</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>n-mc-bb-g-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NC-MC-0-G</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>nc-mc-0-g-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SC010</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sds0098es_solo_a10_iss_2.1.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>231</v>
       </c>
     </row>
   </sheetData>

--- a/data/Inventario_Manuales.xlsx
+++ b/data/Inventario_Manuales.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -563,14 +563,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Ingestado en Supabase</t>
+          <t>109 ingestados en Supabase + CAD-171 (s54): parse OK, ingesta DIFERIDA</t>
         </is>
       </c>
     </row>
@@ -710,45 +710,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -763,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3175,14 +3136,114 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Total: 109 productos</t>
-        </is>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>119 documentos</t>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CAD-171</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Datasheet_CAD-171-DS-736-es.pdf</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CAD-171</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Datasheet-CAD-171-DS-737-en.pdf</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CAD-171</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Manual_CAD-171-MI-716-es.pdf</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>7317</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CAD-171</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Manual configuración</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-Configuracion-MC-380-es-2026-c.pdf</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>32329</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CAD-171</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Manual software configuración</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-software-configuracion-MS-416-es-2026-b.pdf</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11613</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>Total: 110 productos</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>124 documentos</t>
         </is>
       </c>
     </row>

--- a/data/Inventario_Manuales.xlsx
+++ b/data/Inventario_Manuales.xlsx
@@ -563,14 +563,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>109 ingestados en Supabase + CAD-171 (s54): parse OK, ingesta DIFERIDA</t>
+          <t>109 ingestados en Supabase + CAD-171/201/201-PLUS (s54-55): parse OK, ingesta DIFERIDA</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3135,6 +3135,7 @@
         <v>977</v>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -3236,14 +3237,214 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>Total: 110 productos</t>
-        </is>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>124 documentos</t>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CAD-201</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Datasheet_CAD-201-DS-740-es.pdf</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CAD-201</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Datasheet_CAD-201-DS-741-en.pdf</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CAD-201</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Manual_CAD-201-MI-715-es.pdf</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>8385</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CAD-201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Manual configuración</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-Configuracion-MC-380-es-2026-c.pdf</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>32329</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CAD-201</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Manual software configuración</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-software-configuracion-MS-416-es-2026-b.pdf</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11613</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CAD-201-PLUS</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Datasheet_CAD-201-DS-740-es.pdf</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>6719</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CAD-201-PLUS</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Datasheet_CAD-201-DS-741-en.pdf</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CAD-201-PLUS</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Manual_CAD-201-MI-715-es.pdf</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>8385</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CAD-201-PLUS</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Manual configuración</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-Configuracion-MC-380-es-2026-c.pdf</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>32329</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CAD-201-PLUS</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Manual software configuración</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CAD-250_Manual-software-configuracion-MS-416-es-2026-b.pdf</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11613</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>Total: 112 productos</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>134 documentos</t>
         </is>
       </c>
     </row>

--- a/data/Inventario_Manuales.xlsx
+++ b/data/Inventario_Manuales.xlsx
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C6" t="n">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3135,7 +3135,6 @@
         <v>977</v>
       </c>
     </row>
-    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -3459,7 +3458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F373"/>
+  <dimension ref="A1:F370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3865,7 +3864,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Lite&amp;Plus - QR</t>
+          <t>Docs Morley-IAS Max - QR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3885,22 +3884,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Lite&amp;Plus - QR.pdf</t>
+          <t>Docs Morley-IAS Max - QR.pdf</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Max - QR</t>
+          <t>DXc_Guia de instalacion_multiling</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3915,22 +3914,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Max - QR.pdf</t>
+          <t>DXc_Guia de instalacion_multiling.pdf</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>81</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DXc_Guia de instalacion_multiling</t>
+          <t>DXc_Guia de usuario_multiling</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Manual instalación</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3945,17 +3944,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DXc_Guia de instalacion_multiling.pdf</t>
+          <t>DXc_Guia de usuario_multiling.pdf</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>310</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DXc_Guia de usuario_multiling</t>
+          <t>DXc_Manual de configuracion</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3975,22 +3974,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DXc_Guia de usuario_multiling.pdf</t>
+          <t>DXc_Manual de configuracion.pdf</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>253</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DXc_Manual de configuracion</t>
+          <t>DXc_Manual de usuario</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual usuario</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4005,22 +4004,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DXc_Manual de configuracion.pdf</t>
+          <t>DXc_Manual de usuario.pdf</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2425</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DXc_Manual de usuario</t>
+          <t>DXc_Manual variaciones de mercado</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Manual usuario</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4035,17 +4034,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DXc_Manual de usuario.pdf</t>
+          <t>DXc_Manual variaciones de mercado.pdf</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4547</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DXc_Manual variaciones de mercado</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4065,17 +4064,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DXc_Manual variaciones de mercado.pdf</t>
+          <t>Enlace entre TG.pdf</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>F5000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4095,17 +4094,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Enlace entre TG.pdf</t>
+          <t>F5K-2H-UserGuide-SPANISH_Manual F5000.pdf</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>93</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F5000</t>
+          <t>F5K-Additional-Information-Spanish</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4125,17 +4124,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>F5K-2H-UserGuide-SPANISH_Manual F5000.pdf</t>
+          <t>F5K-Additional-Information-Spanish.pdf</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>352</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F5K-Additional-Information-Spanish</t>
+          <t xml:space="preserve">FAAST </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4155,11 +4154,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>F5K-Additional-Information-Spanish.pdf</t>
+          <t>FAAST Area Coverage Planner_SP.pdf</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1275</v>
+        <v>557</v>
       </c>
     </row>
     <row r="24">
@@ -4185,22 +4184,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FAAST Area Coverage Planner_SP.pdf</t>
+          <t>FAAST Understanding EN54-20_SP.pdf</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>557</v>
+        <v>881</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAAST </t>
+          <t>NFS_SUPRA_ES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4215,22 +4214,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FAAST Understanding EN54-20_SP.pdf</t>
+          <t>HLSI-MA-025 Guia Rapida NFS_Supra_ES.pdf</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>881</v>
+        <v>555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NFS_SUPRA_ES</t>
+          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4245,17 +4244,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HLSI-MA-025 Guia Rapida NFS_Supra_ES.pdf</t>
+          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr.pdf</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr</t>
+          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4275,22 +4274,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr.pdf</t>
+          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr.pdf</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>558</v>
+        <v>537</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4305,11 +4304,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr.pdf</t>
+          <t>HLSI-MA-192_05 Guia Rapida UCIP GPRS_SP.pdf</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>537</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29">
@@ -4335,22 +4334,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HLSI-MA-192_05 Guia Rapida UCIP GPRS_SP.pdf</t>
+          <t>HLSI-MA-192_05 Quick Start Guide UCIP GPRS_GB.pdf</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>526</v>
+        <v>573</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>HLSI-MN-025-I_NFS Supra Series</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4365,17 +4364,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HLSI-MA-192_05 Quick Start Guide UCIP GPRS_GB.pdf</t>
+          <t>HLSI-MN-025-I_NFS Supra Series.pdf</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>573</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HLSI-MN-025-I_NFS Supra Series</t>
+          <t>HLSI-MN-025_NFS Supra</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4395,17 +4394,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HLSI-MN-025-I_NFS Supra Series.pdf</t>
+          <t>HLSI-MN-025_NFS Supra.pdf</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1769</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HLSI-MN-025_NFS Supra</t>
+          <t>HLSI-MN-103_RP1r-Supra_lr</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4425,17 +4424,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HLSI-MN-025_NFS Supra.pdf</t>
+          <t>HLSI-MN-103_RP1r-Supra_lr.pdf</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3302</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HLSI-MN-103_RP1r-Supra_lr</t>
+          <t>HLSI-MN-103I_RP1r-Supra_lr</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4455,17 +4454,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HLSI-MN-103_RP1r-Supra_lr.pdf</t>
+          <t>HLSI-MN-103I_RP1r-Supra_lr.pdf</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1662</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HLSI-MN-103I_RP1r-Supra_lr</t>
+          <t>HLSI-MN-192_UCIP</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4485,17 +4484,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HLSI-MN-103I_RP1r-Supra_lr.pdf</t>
+          <t>HLSI-MN-192_UCIP.pdf</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2469</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HLSI-MN-192_UCIP</t>
+          <t>HLSI-MN-963_POL-200-TS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4515,17 +4514,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HLSI-MN-192_UCIP.pdf</t>
+          <t>HLSI-MN-963_POL-200-TS.pdf</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1317</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HLSI-MN-963_POL-200-TS</t>
+          <t>HLSI-TI-007_VSN-4REL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4545,17 +4544,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HLSI-MN-963_POL-200-TS.pdf</t>
+          <t>HLSI-TI-007_VSN-4REL.pdf</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1112</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HLSI-TI-007_VSN-4REL</t>
+          <t>HLSI_MN1007</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4575,17 +4574,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HLSI-TI-007_VSN-4REL.pdf</t>
+          <t>HLSI_MN1007.pdf</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>316</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HLSI_MN1007</t>
+          <t>HSR-E24_Multi</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4605,17 +4604,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HLSI_MN1007.pdf</t>
+          <t>HSR-E24_Multi.pdf</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>372</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HSR-E24_Multi</t>
+          <t>HSR-INT24_Multi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4635,17 +4634,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HSR-E24_Multi.pdf</t>
+          <t>HSR-INT24_Multi.pdf</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HSR-INT24_Multi</t>
+          <t>ECO1002</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4665,17 +4664,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HSR-INT24_Multi.pdf</t>
+          <t>I56-1651-023 ECO1002.pdf</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>19</v>
+        <v>273</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ECO1002</t>
+          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4695,17 +4694,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I56-1651-023 ECO1002.pdf</t>
+          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T.pdf</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>273</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T</t>
+          <t>ECO1003</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4725,17 +4724,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T.pdf</t>
+          <t>I56-1653-022 ECO1003.pdf</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>222</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ECO1003</t>
+          <t>I56-1749-020 ECO1000BREL12L_12NL_24L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4755,17 +4754,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I56-1653-022 ECO1003.pdf</t>
+          <t>I56-1749-020 ECO1000BREL12L_12NL_24L.pdf</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>244</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>I56-1749-020 ECO1000BREL12L_12NL_24L</t>
+          <t>I56-1756-000_400 Series Bases</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4785,17 +4784,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I56-1749-020 ECO1000BREL12L_12NL_24L.pdf</t>
+          <t>I56-1756-000_400 Series Bases.pdf</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>406</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>I56-1756-000_400 Series Bases</t>
+          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4815,17 +4814,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I56-1756-000_400 Series Bases.pdf</t>
+          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO.pdf</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>176</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO</t>
+          <t>I56-2081-012 6500R(S)_ES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4845,17 +4844,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO.pdf</t>
+          <t>I56-2081-012 6500R(S)_ES.pdf</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>234</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>I56-2081-012 6500R(S)_ES</t>
+          <t>MI-DCZM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4875,17 +4874,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I56-2081-012 6500R(S)_ES.pdf</t>
+          <t>I56-2128-003 MI-DCZM.pdf</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>439</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MI-DCZM</t>
+          <t>I56-2954-000_prelim</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4905,17 +4904,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I56-2128-003 MI-DCZM.pdf</t>
+          <t>I56-2954-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>179</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>I56-2954-000_prelim</t>
+          <t>I56-2955-000_prelim</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4935,17 +4934,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I56-2954-000_prelim.pdf</t>
+          <t>I56-2955-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>385</v>
+        <v>330</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>I56-2955-000_prelim</t>
+          <t>I56-2957-000_prelim</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4965,17 +4964,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I56-2955-000_prelim.pdf</t>
+          <t>I56-2957-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>I56-2957-000_prelim</t>
+          <t>I56-3879-000 MI-LPB2-S2I_EN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4985,7 +4984,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4995,27 +4994,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I56-2957-000_prelim.pdf</t>
+          <t>I56-3879-000 MI-LPB2-S2I_EN.pdf</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_EN</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5025,22 +5024,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_EN.pdf</t>
+          <t>I56-3888-010 FAAST LT-200 Adv Guide.pdf</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>320</v>
+        <v>962</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>MI-GATE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guía</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5055,17 +5054,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>I56-3888-010 FAAST LT-200 Adv Guide.pdf</t>
+          <t>I56-4259-000 MI-Gate Gateway.pdf</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>962</v>
+        <v>677</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MI-GATE</t>
+          <t>MI-DMMIE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5085,17 +5084,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I56-4259-000 MI-Gate Gateway.pdf</t>
+          <t>I56-4406-001 MI-DMMIE MI-DMM2IE MI-D2ICMOE.pdf</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>677</v>
+        <v>614</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MI-DMMIE</t>
+          <t>MI-DCMOE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5115,17 +5114,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>I56-4406-001 MI-DMMIE MI-DMM2IE MI-D2ICMOE.pdf</t>
+          <t>I56-4407-001 MI-DCMOE.pdf</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MI-DCMOE</t>
+          <t>I56-4428-000 MI-D240CMOE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5145,17 +5144,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>I56-4407-001 MI-DCMOE.pdf</t>
+          <t>I56-4428-000 MI-D240CMOE.pdf</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>618</v>
+        <v>749</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>I56-4428-000 MI-D240CMOE</t>
+          <t>I56-5002-000-Morley-Strobe</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5175,17 +5174,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>I56-4428-000 MI-D240CMOE.pdf</t>
+          <t>I56-5002-000-Morley-Strobe.pdf</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>749</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>I56-5002-000-Morley-Strobe</t>
+          <t>I56-5003-000-Morley-Sounder-Strobe</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5205,27 +5204,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>I56-5002-000-Morley-Strobe.pdf</t>
+          <t>I56-5003-000-Morley-Sounder-Strobe.pdf</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1784</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>I56-5003-000-Morley-Sounder-Strobe</t>
+          <t>FAAST-LT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5235,17 +5234,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>I56-5003-000-Morley-Sounder-Strobe.pdf</t>
+          <t>I56-6574-005_EN-HS-Stand-Alone-FAAST-LT-200-QIG.pdf</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2167</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FAAST-LT</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5255,7 +5254,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5265,17 +5264,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>I56-6574-005_EN-HS-Stand-Alone-FAAST-LT-200-QIG.pdf</t>
+          <t>I56-6574-005_ES -HS Stand Alone FAAST LT-200 QIG.pdf</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2371</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>FAAST-LT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5285,7 +5284,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5295,17 +5294,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>I56-6574-005_ES -HS Stand Alone FAAST LT-200 QIG.pdf</t>
+          <t>I56-6575-005_EN-FAAST-LT-200-Loop-QIG.pdf</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2223</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FAAST-LT</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5315,7 +5314,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5325,22 +5324,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>I56-6575-005_EN-FAAST-LT-200-Loop-QIG.pdf</t>
+          <t>I56-6575-005_ES FAAST LT-200 Loop QIG.pdf</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2485</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>VSN_MULTI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5355,17 +5354,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>I56-6575-005_ES FAAST LT-200 Loop QIG.pdf</t>
+          <t>Instrucciones_PUL-VSN_MULTI.pdf</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2299</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>VSN_MULTI</t>
+          <t>IRK-2E</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5385,17 +5384,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Instrucciones_PUL-VSN_MULTI.pdf</t>
+          <t>IRK-2E.pdf</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1309</v>
+        <v>240</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IRK-2E</t>
+          <t>LEER PRIMERO_MADT951_10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5415,22 +5414,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IRK-2E.pdf</t>
+          <t>LEER PRIMERO_MADT951_10.pdf</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LEER PRIMERO_MADT951_10</t>
+          <t>Manual SIMEI-HLSI_SP-EN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual técnico</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5445,22 +5444,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LEER PRIMERO_MADT951_10.pdf</t>
+          <t>Manual SIMEI-HLSI_SP-EN.pdf</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>208</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Manual SIMEI-HLSI_SP-EN</t>
+          <t>MIE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Manual técnico</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5475,11 +5474,11 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Manual SIMEI-HLSI_SP-EN.pdf</t>
+          <t>MIE-MI-160rv03.pdf</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2148</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68">
@@ -5505,11 +5504,11 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MIE-MI-160rv03.pdf</t>
+          <t>MIE-MI-320.pdf</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>380</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69">
@@ -5535,11 +5534,11 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MIE-MI-320.pdf</t>
+          <t>MIE-MI-330.pdf</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70">
@@ -5565,11 +5564,11 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MIE-MI-330.pdf</t>
+          <t>MIE-MI-340.pdf</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
@@ -5595,11 +5594,11 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MIE-MI-340.pdf</t>
+          <t>MIE-MI-390.pdf</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72">
@@ -5625,11 +5624,11 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MIE-MI-390.pdf</t>
+          <t>MIE-MI-431rv2.pdf</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>144</v>
+        <v>270</v>
       </c>
     </row>
     <row r="73">
@@ -5655,11 +5654,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MIE-MI-431rv2.pdf</t>
+          <t>MIE-MI-505rv01.pdf</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>270</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="74">
@@ -5685,11 +5684,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MIE-MI-505rv01.pdf</t>
+          <t>MIE-MI-530rv001.pdf</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1826</v>
+        <v>492</v>
       </c>
     </row>
     <row r="75">
@@ -5715,11 +5714,11 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MIE-MI-530rv001.pdf</t>
+          <t>MIE-MI-591.pdf</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>492</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="76">
@@ -5745,11 +5744,11 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MIE-MI-591.pdf</t>
+          <t>MIE-MI-600.pdf</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1193</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="77">
@@ -5775,11 +5774,11 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MIE-MI-600.pdf</t>
+          <t>MIE-MP-530rv001.pdf</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1291</v>
+        <v>395</v>
       </c>
     </row>
     <row r="78">
@@ -5805,11 +5804,11 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MIE-MP-530rv001.pdf</t>
+          <t>MIE-MP-535rv001.pdf</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>395</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79">
@@ -5835,11 +5834,11 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MIE-MP-535rv001.pdf</t>
+          <t>MIE-MU-530rv001.pdf</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>117</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80">
@@ -5865,11 +5864,11 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MIE-MU-530rv001.pdf</t>
+          <t>MIE-MU-535rv001.pdf</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>226</v>
+        <v>132</v>
       </c>
     </row>
     <row r="81">
@@ -5895,17 +5894,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIE-MU-535rv001.pdf</t>
+          <t>MIE-TI-001.pdf</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MIE</t>
+          <t>MNDT1310</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5925,17 +5924,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MIE-TI-001.pdf</t>
+          <t>MNDT1310.pdf</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>84</v>
+        <v>310</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MNDT1310</t>
+          <t>MNDT1311</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5955,22 +5954,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MNDT1310.pdf</t>
+          <t>MNDT1311.pdf</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MNDT1311</t>
+          <t>PSU User Manual_MLT LNG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual usuario</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5985,22 +5984,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MNDT1311.pdf</t>
+          <t>PSU User Manual_MLT LNG.pdf</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>312</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PSU User Manual_MLT LNG</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Manual usuario</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6015,11 +6014,11 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PSU User Manual_MLT LNG.pdf</t>
+          <t>Tg-Honeywell_Introduccion.pdf</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>3083</v>
+        <v>471</v>
       </c>
     </row>
     <row r="86">
@@ -6045,11 +6044,11 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tg-Honeywell_Introduccion.pdf</t>
+          <t>Tg-Honeywell_Tecnico.pdf</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>471</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="87">
@@ -6075,22 +6074,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tg-Honeywell_Tecnico.pdf</t>
+          <t>TG-Honeywell_Usuario.pdf</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2271</v>
+        <v>866</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>F5000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6100,27 +6099,27 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>publico</t>
+          <t>privado</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TG-Honeywell_Usuario.pdf</t>
+          <t>0044-033-01 Guia F5000.pdf</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>866</v>
+        <v>894</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>F5000</t>
+          <t>27012012 ETIQUETA INSTRUCCIONES VISION SUPRA REV A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Guía</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6135,17 +6134,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0044-033-01 Guia F5000.pdf</t>
+          <t>27012012 ETIQUETA INSTRUCCIONES VISION SUPRA REV A .pdf</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>894</v>
+        <v>471</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>27012012 ETIQUETA INSTRUCCIONES VISION SUPRA REV A</t>
+          <t>30012012  TARJETAS IDIOMAS VISION SUPRA rev A</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6165,17 +6164,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>27012012 ETIQUETA INSTRUCCIONES VISION SUPRA REV A .pdf</t>
+          <t>30012012  TARJETAS IDIOMAS VISION SUPRA rev A.pdf</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>471</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30012012  TARJETAS IDIOMAS VISION SUPRA rev A</t>
+          <t>996-130-000-3 Manuel d'utilisation ZX_hlsi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6195,17 +6194,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>30012012  TARJETAS IDIOMAS VISION SUPRA rev A.pdf</t>
+          <t>996-130-000-3 Manuel d'utilisation ZX_hlsi.pdf</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>44</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>996-130-000-3 Manuel d'utilisation ZX_hlsi</t>
+          <t>FAAST FLEX</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6225,17 +6224,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>996-130-000-3 Manuel d'utilisation ZX_hlsi.pdf</t>
+          <t>A05-7030-100_B_ES_Morley FAAST FLEX Addressable.pdf</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>333</v>
+        <v>10134</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FAAST FLEX</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6255,17 +6254,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>A05-7030-100_B_ES_Morley FAAST FLEX Addressable.pdf</t>
+          <t>Actulización histórico TG.pdf</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>10134</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>ASD Cold Environments_SP</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6285,17 +6284,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Actulización histórico TG.pdf</t>
+          <t>ASD Cold Environments_SP.pdf</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>60</v>
+        <v>3815</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ASD Cold Environments_SP</t>
+          <t>ASD Harsh Environments_SP</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6315,17 +6314,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ASD Cold Environments_SP.pdf</t>
+          <t>ASD Harsh Environments_SP.pdf</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>3815</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ASD Harsh Environments_SP</t>
+          <t>Cursos formacion_Marzo 2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6345,17 +6344,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ASD Harsh Environments_SP.pdf</t>
+          <t>Cursos formacion_Marzo 2026.pdf</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2368</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cursos formacion_Marzo 2026</t>
+          <t>D 1150-1 BRH Morley</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6375,17 +6374,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cursos formacion_Marzo 2026.pdf</t>
+          <t>D 1150-1 BRH Morley.pdf</t>
         </is>
       </c>
       <c r="F97" t="n">
-        <v>247</v>
+        <v>939</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D 1150-1 BRH Morley</t>
+          <t>D 1151-1 BRS Morley</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6405,17 +6404,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>D 1150-1 BRH Morley.pdf</t>
+          <t>D 1151-1 BRS Morley.pdf</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>D 1151-1 BRS Morley</t>
+          <t>D 1152-1 BGL Morley</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6435,17 +6434,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>D 1151-1 BRS Morley.pdf</t>
+          <t>D 1152-1 BGL Morley.pdf</t>
         </is>
       </c>
       <c r="F99" t="n">
-        <v>935</v>
+        <v>879</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>D 1152-1 BGL Morley</t>
+          <t xml:space="preserve">D391 Issue 3 WR2001 </t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6465,17 +6464,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>D 1152-1 BGL Morley.pdf</t>
+          <t>D391 Issue 3 WR2001 .pdf</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>879</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">D391 Issue 3 WR2001 </t>
+          <t>D707 issue 1 - MI-MCPA5_Eng</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6495,17 +6494,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>D391 Issue 3 WR2001 .pdf</t>
+          <t>D707 issue 1 - MI-MCPA5_Eng.pdf</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>206</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>D707 issue 1 - MI-MCPA5_Eng</t>
+          <t>Docs Morley-IAS Max - QR</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6525,22 +6524,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>D707 issue 1 - MI-MCPA5_Eng.pdf</t>
+          <t>Docs Morley-IAS Max - QR.pdf</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Lite&amp;Plus - QR</t>
+          <t>DXc_Guia de instalacion_multiling</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual instalación</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6555,17 +6554,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Lite&amp;Plus - QR.pdf</t>
+          <t>DXc_Guia de instalacion_multiling.pdf</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>80</v>
+        <v>310</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Max - QR</t>
+          <t>DXc_Guia de usuario_multiling</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6585,22 +6584,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Docs Morley-IAS Max - QR.pdf</t>
+          <t>DXc_Guia de usuario_multiling.pdf</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>81</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>DXc_Guia de instalacion_multiling</t>
+          <t>DXc_Manual de configuracion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Manual instalación</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6615,22 +6614,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DXc_Guia de instalacion_multiling.pdf</t>
+          <t>DXc_Manual de configuracion.pdf</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>310</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DXc_Guia de usuario_multiling</t>
+          <t>DXc_Manual de usuario</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual usuario</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6645,17 +6644,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>DXc_Guia de usuario_multiling.pdf</t>
+          <t>DXc_Manual de usuario.pdf</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>253</v>
+        <v>4547</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DXc_Manual de configuracion</t>
+          <t>DXc_Manual variaciones de mercado</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6675,22 +6674,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DXc_Manual de configuracion.pdf</t>
+          <t>DXc_Manual variaciones de mercado.pdf</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2425</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DXc_Manual de usuario</t>
+          <t>E56-6515ES-000_Morley_MI-OSI-RIE_Installation_Guid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Manual usuario</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6705,17 +6704,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>DXc_Manual de usuario.pdf</t>
+          <t>E56-6515ES-000_Morley_MI-OSI-RIE_Installation_Guide.pdf</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>4547</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DXc_Manual variaciones de mercado</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6735,17 +6734,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>DXc_Manual variaciones de mercado.pdf</t>
+          <t>Enlace entre TG.pdf</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>214</v>
+        <v>93</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>E56-6515ES-000_Morley_MI-OSI-RIE_Installation_Guid</t>
+          <t>F5000</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6765,17 +6764,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>E56-6515ES-000_Morley_MI-OSI-RIE_Installation_Guide.pdf</t>
+          <t>F5K-2H-UserGuide-SPANISH_Manual F5000.pdf</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>2553</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>F5K-Additional-Information-Spanish</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6795,17 +6794,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enlace entre TG.pdf</t>
+          <t>F5K-Additional-Information-Spanish.pdf</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>93</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>F5000</t>
+          <t xml:space="preserve">FAAST </t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -6825,17 +6824,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>F5K-2H-UserGuide-SPANISH_Manual F5000.pdf</t>
+          <t>FAAST Area Coverage Planner_SP.pdf</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>352</v>
+        <v>557</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>F5K-Additional-Information-Spanish</t>
+          <t xml:space="preserve">FAAST </t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -6855,22 +6854,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>F5K-Additional-Information-Spanish.pdf</t>
+          <t>FAAST Understanding EN54-20_SP.pdf</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1275</v>
+        <v>881</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAAST </t>
+          <t>MIW</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6885,22 +6884,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FAAST Area Coverage Planner_SP.pdf</t>
+          <t>Guia Serie MIW.pdf</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>557</v>
+        <v>5619</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">FAAST </t>
+          <t>NFS_SUPRA_ES</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6915,22 +6914,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>FAAST Understanding EN54-20_SP.pdf</t>
+          <t>HLSI-MA-025 Guia Rapida NFS_Supra_ES.pdf</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>881</v>
+        <v>555</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MIW</t>
+          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Guía</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6945,22 +6944,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Guia Serie MIW.pdf</t>
+          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr.pdf</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>5619</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NFS_SUPRA_ES</t>
+          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6975,22 +6974,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HLSI-MA-025 Guia Rapida NFS_Supra_ES.pdf</t>
+          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr.pdf</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>555</v>
+        <v>537</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7005,22 +7004,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>HLSI-MA-103-I_GuiaRapida_RP1r-Supra_EN_lr.pdf</t>
+          <t>HLSI-MA-192_05 Guia Rapida UCIP GPRS_SP.pdf</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>558</v>
+        <v>526</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7035,22 +7034,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HLSI-MA-103_GuiaRapida_RP1r-Supra_ES_lr.pdf</t>
+          <t>HLSI-MA-192_05 Quick Start Guide UCIP GPRS_GB.pdf</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>537</v>
+        <v>573</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>HLSI-MI-130F</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7065,22 +7064,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HLSI-MA-192_05 Guia Rapida UCIP GPRS_SP.pdf</t>
+          <t>HLSI-MI-130F.pdf</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>526</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>HLSI-MI-130I</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7095,17 +7094,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HLSI-MA-192_05 Quick Start Guide UCIP GPRS_GB.pdf</t>
+          <t>HLSI-MI-130I.pdf</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>573</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>HLSI-MI-130F</t>
+          <t>HLSI-MI-580I</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7125,17 +7124,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HLSI-MI-130F.pdf</t>
+          <t>HLSI-MI-580I.pdf</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>1519</v>
+        <v>673</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HLSI-MI-130I</t>
+          <t>HLSI-MN-025-I_NFS Supra Series</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7155,17 +7154,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HLSI-MI-130I.pdf</t>
+          <t>HLSI-MN-025-I_NFS Supra Series.pdf</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1500</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HLSI-MI-580I</t>
+          <t>HLSI-MN-025_NFS Supra</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7185,17 +7184,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HLSI-MI-580I.pdf</t>
+          <t>HLSI-MN-025_NFS Supra.pdf</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>673</v>
+        <v>3302</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>HLSI-MN-025-I_NFS Supra Series</t>
+          <t>HLSI-MN-103_RP1r-Supra_lr</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -7215,17 +7214,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HLSI-MN-025-I_NFS Supra Series.pdf</t>
+          <t>HLSI-MN-103_RP1r-Supra_lr.pdf</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1769</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HLSI-MN-025_NFS Supra</t>
+          <t>HLSI-MN-103I_RP1r-Supra_lr</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7245,17 +7244,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HLSI-MN-025_NFS Supra.pdf</t>
+          <t>HLSI-MN-103I_RP1r-Supra_lr.pdf</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>3302</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>HLSI-MN-103_RP1r-Supra_lr</t>
+          <t>HLSI-MN-192_UCIP</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7275,17 +7274,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HLSI-MN-103_RP1r-Supra_lr.pdf</t>
+          <t>HLSI-MN-192_UCIP.pdf</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1662</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HLSI-MN-103I_RP1r-Supra_lr</t>
+          <t>HLSI-MN-963_POL-200-TS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7305,17 +7304,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HLSI-MN-103I_RP1r-Supra_lr.pdf</t>
+          <t>HLSI-MN-963_POL-200-TS.pdf</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2469</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HLSI-MN-192_UCIP</t>
+          <t>HLSI-TI-007_VSN-4REL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7335,17 +7334,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HLSI-MN-192_UCIP.pdf</t>
+          <t>HLSI-TI-007_VSN-4REL.pdf</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>1317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HLSI-MN-963_POL-200-TS</t>
+          <t>HLSI_MA102_bis2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7365,17 +7364,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HLSI-MN-963_POL-200-TS.pdf</t>
+          <t>HLSI_MA102_bis2.pdf</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>1112</v>
+        <v>171</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HLSI-TI-007_VSN-4REL</t>
+          <t>HLSI_MN1007</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7395,17 +7394,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HLSI-TI-007_VSN-4REL.pdf</t>
+          <t>HLSI_MN1007.pdf</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>316</v>
+        <v>372</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HLSI_MA102_bis2</t>
+          <t>HSR-E24_Multi</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7425,17 +7424,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HLSI_MA102_bis2.pdf</t>
+          <t>HSR-E24_Multi.pdf</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>171</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HLSI_MN1007</t>
+          <t>HSR-INT24_Multi</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7455,17 +7454,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HLSI_MN1007.pdf</t>
+          <t>HSR-INT24_Multi.pdf</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>372</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HSR-E24_Multi</t>
+          <t>ECO1002</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7485,17 +7484,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>HSR-E24_Multi.pdf</t>
+          <t>I56-1651-023 ECO1002.pdf</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>20</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HSR-INT24_Multi</t>
+          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7515,17 +7514,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HSR-INT24_Multi.pdf</t>
+          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T.pdf</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>19</v>
+        <v>222</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ECO1002</t>
+          <t>ECO1003</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7545,17 +7544,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>I56-1651-023 ECO1002.pdf</t>
+          <t>I56-1653-022 ECO1003.pdf</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>273</v>
+        <v>244</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T</t>
+          <t>MI-PTSE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7575,17 +7574,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>I56-1652-023 ECO1005_ECO1005T_ECO1004T.pdf</t>
+          <t>I56-1657-001 MI-PTSE.pdf</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>222</v>
+        <v>276</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ECO1003</t>
+          <t>I56-1749-020 ECO1000BREL12L_12NL_24L</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7605,17 +7604,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>I56-1653-022 ECO1003.pdf</t>
+          <t>I56-1749-020 ECO1000BREL12L_12NL_24L.pdf</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>244</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MI-PTSE</t>
+          <t>I56-1756-000_400 Series Bases</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7635,17 +7634,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>I56-1657-001 MI-PTSE.pdf</t>
+          <t>I56-1756-000_400 Series Bases.pdf</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>276</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>I56-1749-020 ECO1000BREL12L_12NL_24L</t>
+          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7665,17 +7664,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>I56-1749-020 ECO1000BREL12L_12NL_24L.pdf</t>
+          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO.pdf</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>406</v>
+        <v>234</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>I56-1756-000_400 Series Bases</t>
+          <t>I56-2081-012 6500R(S)_ES</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7695,17 +7694,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>I56-1756-000_400 Series Bases.pdf</t>
+          <t>I56-2081-012 6500R(S)_ES.pdf</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>176</v>
+        <v>439</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO</t>
+          <t>I56-2082-013 MI-LPB2_ES</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7725,17 +7724,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>I56-2006-004 MI-DMMI_DMM2I_D2ICMO.pdf</t>
+          <t>I56-2082-013 MI-LPB2_ES.pdf</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>234</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>I56-2081-012 6500R(S)_ES</t>
+          <t>I56-2082-013 MI-LPB2_ES_1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7755,17 +7754,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>I56-2081-012 6500R(S)_ES.pdf</t>
+          <t>I56-2082-013 MI-LPB2_ES_1.pdf</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>439</v>
+        <v>466</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>I56-2082-013 MI-LPB2_ES</t>
+          <t>MI-DCZM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7785,17 +7784,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>I56-2082-013 MI-LPB2_ES.pdf</t>
+          <t>I56-2128-003 MI-DCZM.pdf</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>467</v>
+        <v>179</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>I56-2082-013 MI-LPB2_ES_1</t>
+          <t>I56-2954-000_prelim</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7815,17 +7814,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>I56-2082-013 MI-LPB2_ES_1.pdf</t>
+          <t>I56-2954-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>466</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MI-DCZM</t>
+          <t>I56-2955-000_prelim</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7845,17 +7844,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>I56-2128-003 MI-DCZM.pdf</t>
+          <t>I56-2955-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>179</v>
+        <v>330</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>I56-2954-000_prelim</t>
+          <t>I56-2956-000_prelim</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7875,17 +7874,17 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>I56-2954-000_prelim.pdf</t>
+          <t>I56-2956-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>385</v>
+        <v>617</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>I56-2955-000_prelim</t>
+          <t>I56-2957-000_prelim</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7905,17 +7904,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>I56-2955-000_prelim.pdf</t>
+          <t>I56-2957-000_prelim.pdf</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>I56-2956-000_prelim</t>
+          <t>I56-3879-000 MI-LPB2-S2I_EN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7925,7 +7924,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7935,17 +7934,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>I56-2956-000_prelim.pdf</t>
+          <t>I56-3879-000 MI-LPB2-S2I_EN.pdf</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>617</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>I56-2957-000_prelim</t>
+          <t>I56-3879-000 MI-LPB2-S2I_ES</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7965,27 +7964,27 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>I56-2957-000_prelim.pdf</t>
+          <t>I56-3879-000 MI-LPB2-S2I_ES.pdf</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_EN</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7995,22 +7994,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_EN.pdf</t>
+          <t>I56-3888-010 FAAST LT-200 Adv Guide.pdf</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>320</v>
+        <v>962</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_ES</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -8025,11 +8024,11 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>I56-3879-000 MI-LPB2-S2I_ES.pdf</t>
+          <t>I56-3956-201_ES Morley Loop FAAST LT QIG.pdf</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>315</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="153">
@@ -8040,7 +8039,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Guía</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -8055,22 +8054,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>I56-3888-010 FAAST LT-200 Adv Guide.pdf</t>
+          <t>I56-3956-201_PT Morley Loop FAAST LT QIG.pdf</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>962</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>I56-3991-000 MI-MM3E-S2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -8085,22 +8084,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>I56-3956-201_ES Morley Loop FAAST LT QIG.pdf</t>
+          <t>I56-3991-000 MI-MM3E-S2.pdf</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1651</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>MI-GATE</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -8115,17 +8114,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>I56-3956-201_PT Morley Loop FAAST LT QIG.pdf</t>
+          <t>I56-4259-000 MI-Gate Gateway.pdf</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1742</v>
+        <v>677</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>I56-3991-000 MI-MM3E-S2</t>
+          <t>MI-DMMIE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8145,17 +8144,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>I56-3991-000 MI-MM3E-S2.pdf</t>
+          <t>I56-4406-001 MI-DMMIE MI-DMM2IE MI-D2ICMOE.pdf</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1322</v>
+        <v>614</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MI-GATE</t>
+          <t>MI-DCMOE</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8175,17 +8174,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>I56-4259-000 MI-Gate Gateway.pdf</t>
+          <t>I56-4407-001 MI-DCMOE.pdf</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>677</v>
+        <v>618</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MI-DMMIE</t>
+          <t>I56-4428-000 MI-D240CMOE</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8205,17 +8204,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>I56-4406-001 MI-DMMIE MI-DMM2IE MI-D2ICMOE.pdf</t>
+          <t>I56-4428-000 MI-D240CMOE.pdf</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>614</v>
+        <v>749</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MI-DCMOE</t>
+          <t>I56-5002-000-Morley-Strobe</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8235,17 +8234,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>I56-4407-001 MI-DCMOE.pdf</t>
+          <t>I56-5002-000-Morley-Strobe.pdf</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>618</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>I56-4428-000 MI-D240CMOE</t>
+          <t>I56-5003-000-Morley-Sounder-Strobe</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8265,27 +8264,27 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>I56-4428-000 MI-D240CMOE.pdf</t>
+          <t>I56-5003-000-Morley-Sounder-Strobe.pdf</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>749</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>I56-5002-000-Morley-Strobe</t>
+          <t>FAAST-LT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8295,22 +8294,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>I56-5002-000-Morley-Strobe.pdf</t>
+          <t>I56-6574-005_EN-HS-Stand-Alone-FAAST-LT-200-QIG.pdf</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>1784</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>I56-5003-000-Morley-Sounder-Strobe</t>
+          <t>FAAST LT</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía rápida</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -8325,11 +8324,11 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>I56-5003-000-Morley-Sounder-Strobe.pdf</t>
+          <t>I56-6574-005_ES -HS Stand Alone FAAST LT-200 QIG.pdf</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>2167</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="163">
@@ -8355,11 +8354,11 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>I56-6574-005_EN-HS-Stand-Alone-FAAST-LT-200-QIG.pdf</t>
+          <t>I56-6575-005_EN-FAAST-LT-200-Loop-QIG.pdf</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>2371</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="164">
@@ -8385,27 +8384,27 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>I56-6574-005_ES -HS Stand Alone FAAST LT-200 QIG.pdf</t>
+          <t>I56-6575-005_ES FAAST LT-200 Loop QIG.pdf</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>2223</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FAAST-LT</t>
+          <t>VSN_MULTI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8415,22 +8414,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>I56-6575-005_EN-FAAST-LT-200-Loop-QIG.pdf</t>
+          <t>Instrucciones_PUL-VSN_MULTI.pdf</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>2485</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FAAST LT</t>
+          <t>IRK-2E</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Guía rápida</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8445,17 +8444,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>I56-6575-005_ES FAAST LT-200 Loop QIG.pdf</t>
+          <t>IRK-2E.pdf</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>2299</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VSN_MULTI</t>
+          <t>IRK-E-SI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8475,17 +8474,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Instrucciones_PUL-VSN_MULTI.pdf</t>
+          <t>IRK-E-SI.pdf</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>1309</v>
+        <v>125</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>IRK-2E</t>
+          <t>LEER PRIMERO_MADT951_10</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8505,22 +8504,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>IRK-2E.pdf</t>
+          <t>LEER PRIMERO_MADT951_10.pdf</t>
         </is>
       </c>
       <c r="F168" t="n">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>IRK-E-SI</t>
+          <t>Manual SIMEI-HLSI_SP-EN</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual técnico</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8535,17 +8534,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>IRK-E-SI.pdf</t>
+          <t>Manual SIMEI-HLSI_SP-EN.pdf</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>125</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LEER PRIMERO_MADT951_10</t>
+          <t>MIE</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8565,22 +8564,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>LEER PRIMERO_MADT951_10.pdf</t>
+          <t>MIE-MA-100_01.pdf</t>
         </is>
       </c>
       <c r="F170" t="n">
-        <v>208</v>
+        <v>549</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Manual SIMEI-HLSI_SP-EN</t>
+          <t>MIE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Manual técnico</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8595,11 +8594,11 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Manual SIMEI-HLSI_SP-EN.pdf</t>
+          <t>MIE-MA-100_02.pdf</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>2148</v>
+        <v>608</v>
       </c>
     </row>
     <row r="172">
@@ -8625,11 +8624,11 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>MIE-MA-100_01.pdf</t>
+          <t>MIE-MA-100_02P.pdf</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>549</v>
+        <v>350</v>
       </c>
     </row>
     <row r="173">
@@ -8655,11 +8654,11 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>MIE-MA-100_02.pdf</t>
+          <t>MIE-MA-300_01.pdf</t>
         </is>
       </c>
       <c r="F173" t="n">
-        <v>608</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="174">
@@ -8685,11 +8684,11 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>MIE-MA-100_02P.pdf</t>
+          <t>MIE-MA-300_02.pdf</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>350</v>
+        <v>46</v>
       </c>
     </row>
     <row r="175">
@@ -8715,11 +8714,11 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>MIE-MA-300_01.pdf</t>
+          <t>MIE-MC-130rv02.pdf</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>1627</v>
+        <v>675</v>
       </c>
     </row>
     <row r="176">
@@ -8745,11 +8744,11 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>MIE-MA-300_02.pdf</t>
+          <t>MIE-MC-300.pdf</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>46</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="177">
@@ -8775,11 +8774,11 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>MIE-MC-130rv02.pdf</t>
+          <t>MIE-MC-350.pdf</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>675</v>
+        <v>130</v>
       </c>
     </row>
     <row r="178">
@@ -8805,11 +8804,11 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>MIE-MC-300.pdf</t>
+          <t>MIE-MC-520.pdf</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>2313</v>
+        <v>686</v>
       </c>
     </row>
     <row r="179">
@@ -8835,11 +8834,11 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>MIE-MC-350.pdf</t>
+          <t>MIE-MC-530.pdf</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>130</v>
+        <v>695</v>
       </c>
     </row>
     <row r="180">
@@ -8865,11 +8864,11 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>MIE-MC-520.pdf</t>
+          <t>MIE-MI-010.pdf</t>
         </is>
       </c>
       <c r="F180" t="n">
-        <v>686</v>
+        <v>354</v>
       </c>
     </row>
     <row r="181">
@@ -8895,11 +8894,11 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MIE-MC-530.pdf</t>
+          <t>MIE-MI-030.pdf</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>695</v>
+        <v>100</v>
       </c>
     </row>
     <row r="182">
@@ -8925,11 +8924,11 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>MIE-MI-010.pdf</t>
+          <t>MIE-MI-100.pdf</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>354</v>
+        <v>5203</v>
       </c>
     </row>
     <row r="183">
@@ -8955,11 +8954,11 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>MIE-MI-030.pdf</t>
+          <t>MIE-MI-110.pdf</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>100</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="184">
@@ -8985,11 +8984,11 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>MIE-MI-100.pdf</t>
+          <t>MIE-MI-120P.pdf</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>5203</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="185">
@@ -9015,11 +9014,11 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>MIE-MI-110.pdf</t>
+          <t>MIE-MI-130P.PDF</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>1761</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="186">
@@ -9045,11 +9044,11 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>MIE-MI-120P.pdf</t>
+          <t>MIE-MI-140.pdf</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>1370</v>
+        <v>442</v>
       </c>
     </row>
     <row r="187">
@@ -9075,11 +9074,11 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>MIE-MI-130P.PDF</t>
+          <t>MIE-MI-160rv03.pdf</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>1656</v>
+        <v>380</v>
       </c>
     </row>
     <row r="188">
@@ -9105,11 +9104,11 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>MIE-MI-140.pdf</t>
+          <t>MIE-MI-220.pdf</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>442</v>
+        <v>189</v>
       </c>
     </row>
     <row r="189">
@@ -9135,11 +9134,11 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>MIE-MI-160rv03.pdf</t>
+          <t>MIE-MI-230.pdf</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>380</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="190">
@@ -9165,11 +9164,11 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>MIE-MI-220.pdf</t>
+          <t>MIE-MI-300rv02.pdf</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>189</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="191">
@@ -9195,11 +9194,11 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>MIE-MI-230.pdf</t>
+          <t>MIE-MI-310.pdf</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1930</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="192">
@@ -9225,11 +9224,11 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>MIE-MI-300rv02.pdf</t>
+          <t>MIE-MI-320.pdf</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>4047</v>
+        <v>115</v>
       </c>
     </row>
     <row r="193">
@@ -9255,11 +9254,11 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>MIE-MI-310.pdf</t>
+          <t>MIE-MI-330.pdf</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>3090</v>
+        <v>143</v>
       </c>
     </row>
     <row r="194">
@@ -9285,11 +9284,11 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>MIE-MI-320.pdf</t>
+          <t>MIE-MI-340.pdf</t>
         </is>
       </c>
       <c r="F194" t="n">
-        <v>115</v>
+        <v>78</v>
       </c>
     </row>
     <row r="195">
@@ -9315,11 +9314,11 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>MIE-MI-330.pdf</t>
+          <t>MIE-MI-340_1.pdf</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>143</v>
+        <v>78</v>
       </c>
     </row>
     <row r="196">
@@ -9345,11 +9344,11 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>MIE-MI-340.pdf</t>
+          <t>MIE-MI-390.pdf</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
     </row>
     <row r="197">
@@ -9375,11 +9374,11 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>MIE-MI-340_1.pdf</t>
+          <t>MIE-MI-430.pdf</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>78</v>
+        <v>169</v>
       </c>
     </row>
     <row r="198">
@@ -9405,11 +9404,11 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>MIE-MI-390.pdf</t>
+          <t>MIE-MI-431rv2.pdf</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>144</v>
+        <v>270</v>
       </c>
     </row>
     <row r="199">
@@ -9435,11 +9434,11 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>MIE-MI-430.pdf</t>
+          <t>MIE-MI-431rv2_1.pdf</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>169</v>
+        <v>270</v>
       </c>
     </row>
     <row r="200">
@@ -9465,11 +9464,11 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>MIE-MI-431rv2.pdf</t>
+          <t>MIE-MI-440.pdf</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>270</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="201">
@@ -9495,11 +9494,11 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>MIE-MI-431rv2_1.pdf</t>
+          <t>MIE-MI-450.pdf</t>
         </is>
       </c>
       <c r="F201" t="n">
-        <v>270</v>
+        <v>130</v>
       </c>
     </row>
     <row r="202">
@@ -9525,11 +9524,11 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>MIE-MI-440.pdf</t>
+          <t>MIE-MI-460.pdf</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>1223</v>
+        <v>18</v>
       </c>
     </row>
     <row r="203">
@@ -9555,11 +9554,11 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>MIE-MI-450.pdf</t>
+          <t>MIE-MI-470.pdf</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>130</v>
+        <v>178</v>
       </c>
     </row>
     <row r="204">
@@ -9585,11 +9584,11 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>MIE-MI-460.pdf</t>
+          <t>MIE-MI-480.pdf</t>
         </is>
       </c>
       <c r="F204" t="n">
-        <v>18</v>
+        <v>207</v>
       </c>
     </row>
     <row r="205">
@@ -9615,11 +9614,11 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>MIE-MI-470.pdf</t>
+          <t>MIE-MI-490.pdf</t>
         </is>
       </c>
       <c r="F205" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="206">
@@ -9645,11 +9644,11 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>MIE-MI-480.pdf</t>
+          <t>MIE-MI-505rv01.pdf</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>207</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="207">
@@ -9675,11 +9674,11 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>MIE-MI-490.pdf</t>
+          <t>MIE-MI-530rv001.pdf</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>187</v>
+        <v>492</v>
       </c>
     </row>
     <row r="208">
@@ -9705,11 +9704,11 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>MIE-MI-505rv01.pdf</t>
+          <t>MIE-MI-560rv01_I.pdf</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>1826</v>
+        <v>570</v>
       </c>
     </row>
     <row r="209">
@@ -9735,11 +9734,11 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>MIE-MI-530rv001.pdf</t>
+          <t>MIE-MI-560rv03.pdf</t>
         </is>
       </c>
       <c r="F209" t="n">
-        <v>492</v>
+        <v>549</v>
       </c>
     </row>
     <row r="210">
@@ -9765,11 +9764,11 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>MIE-MI-560rv01_I.pdf</t>
+          <t>MIE-MI-580.pdf</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>570</v>
+        <v>928</v>
       </c>
     </row>
     <row r="211">
@@ -9795,11 +9794,11 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>MIE-MI-560rv03.pdf</t>
+          <t>MIE-MI-591.pdf</t>
         </is>
       </c>
       <c r="F211" t="n">
-        <v>549</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="212">
@@ -9825,11 +9824,11 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>MIE-MI-580.pdf</t>
+          <t>MIE-MI-600.pdf</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>928</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="213">
@@ -9855,11 +9854,11 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>MIE-MI-591.pdf</t>
+          <t>MIE-MP-210.pdf</t>
         </is>
       </c>
       <c r="F213" t="n">
-        <v>1193</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="214">
@@ -9885,11 +9884,11 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>MIE-MI-600.pdf</t>
+          <t>MIE-MP-230.pdf</t>
         </is>
       </c>
       <c r="F214" t="n">
-        <v>1291</v>
+        <v>5649</v>
       </c>
     </row>
     <row r="215">
@@ -9915,11 +9914,11 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>MIE-MP-210.pdf</t>
+          <t>MIE-MP-305.pdf</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>1323</v>
+        <v>252</v>
       </c>
     </row>
     <row r="216">
@@ -9945,11 +9944,11 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>MIE-MP-230.pdf</t>
+          <t>MIE-MP-310.pdf</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>5649</v>
+        <v>5240</v>
       </c>
     </row>
     <row r="217">
@@ -9975,11 +9974,11 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>MIE-MP-305.pdf</t>
+          <t>MIE-MP-315.pdf</t>
         </is>
       </c>
       <c r="F217" t="n">
-        <v>252</v>
+        <v>118</v>
       </c>
     </row>
     <row r="218">
@@ -10005,11 +10004,11 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>MIE-MP-310.pdf</t>
+          <t>MIE-MP-520rv04.pdf</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>5240</v>
+        <v>967</v>
       </c>
     </row>
     <row r="219">
@@ -10035,11 +10034,11 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>MIE-MP-315.pdf</t>
+          <t>MIE-MP-525rv1.pdf</t>
         </is>
       </c>
       <c r="F219" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="220">
@@ -10065,11 +10064,11 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>MIE-MP-520rv04.pdf</t>
+          <t>MIE-MP-530rv001.pdf</t>
         </is>
       </c>
       <c r="F220" t="n">
-        <v>967</v>
+        <v>395</v>
       </c>
     </row>
     <row r="221">
@@ -10095,11 +10094,11 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>MIE-MP-525rv1.pdf</t>
+          <t>MIE-MP-535rv001.pdf</t>
         </is>
       </c>
       <c r="F221" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222">
@@ -10125,11 +10124,11 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>MIE-MP-530rv001.pdf</t>
+          <t>MIE-MU-215.pdf</t>
         </is>
       </c>
       <c r="F222" t="n">
-        <v>395</v>
+        <v>356</v>
       </c>
     </row>
     <row r="223">
@@ -10155,11 +10154,11 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>MIE-MP-535rv001.pdf</t>
+          <t>MIE-MU-230.pdf</t>
         </is>
       </c>
       <c r="F223" t="n">
-        <v>117</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="224">
@@ -10185,11 +10184,11 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>MIE-MU-215.pdf</t>
+          <t>MIE-MU-300.pdf</t>
         </is>
       </c>
       <c r="F224" t="n">
-        <v>356</v>
+        <v>7116</v>
       </c>
     </row>
     <row r="225">
@@ -10215,11 +10214,11 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>MIE-MU-230.pdf</t>
+          <t>MIE-MU-310.pdf</t>
         </is>
       </c>
       <c r="F225" t="n">
-        <v>1657</v>
+        <v>5078</v>
       </c>
     </row>
     <row r="226">
@@ -10245,11 +10244,11 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MIE-MU-300.pdf</t>
+          <t>MIE-MU-315.pdf</t>
         </is>
       </c>
       <c r="F226" t="n">
-        <v>7116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="227">
@@ -10275,11 +10274,11 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>MIE-MU-310.pdf</t>
+          <t>MIE-MU-520rv02.pdf</t>
         </is>
       </c>
       <c r="F227" t="n">
-        <v>5078</v>
+        <v>500</v>
       </c>
     </row>
     <row r="228">
@@ -10305,11 +10304,11 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>MIE-MU-315.pdf</t>
+          <t>MIE-MU-525rv01.pdf</t>
         </is>
       </c>
       <c r="F228" t="n">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="229">
@@ -10335,11 +10334,11 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>MIE-MU-520rv02.pdf</t>
+          <t>MIE-MU-530rv001.pdf</t>
         </is>
       </c>
       <c r="F229" t="n">
-        <v>500</v>
+        <v>226</v>
       </c>
     </row>
     <row r="230">
@@ -10365,11 +10364,11 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>MIE-MU-525rv01.pdf</t>
+          <t>MIE-MU-535rv001.pdf</t>
         </is>
       </c>
       <c r="F230" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
     </row>
     <row r="231">
@@ -10395,11 +10394,11 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>MIE-MU-530rv001.pdf</t>
+          <t>MIE-MU-610_via radio MIW.pdf</t>
         </is>
       </c>
       <c r="F231" t="n">
-        <v>226</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="232">
@@ -10425,17 +10424,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>MIE-MU-535rv001.pdf</t>
+          <t>MIE-TI-001.pdf</t>
         </is>
       </c>
       <c r="F232" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MIE</t>
+          <t>MIEMA130</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10455,17 +10454,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>MIE-MU-610_via radio MIW.pdf</t>
+          <t>MIEMA130.pdf</t>
         </is>
       </c>
       <c r="F233" t="n">
-        <v>1390</v>
+        <v>128</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MIE</t>
+          <t>MIEMA550_01</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10485,17 +10484,17 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>MIE-TI-001.pdf</t>
+          <t>MIEMA550_01.pdf</t>
         </is>
       </c>
       <c r="F234" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>MIEMA130</t>
+          <t>MIEMI120rev05</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10515,17 +10514,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>MIEMA130.pdf</t>
+          <t>MIEMI120rev05.pdf</t>
         </is>
       </c>
       <c r="F235" t="n">
-        <v>128</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>MIEMA550_01</t>
+          <t>MIEMI130</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10545,17 +10544,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>MIEMA550_01.pdf</t>
+          <t>MIEMI130.pdf</t>
         </is>
       </c>
       <c r="F236" t="n">
-        <v>57</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>MIEMI120rev05</t>
+          <t>MIEMI430P</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10575,17 +10574,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>MIEMI120rev05.pdf</t>
+          <t>MIEMI430P.pdf</t>
         </is>
       </c>
       <c r="F237" t="n">
-        <v>1682</v>
+        <v>63</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MIEMI130</t>
+          <t>MIEMI550</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10605,17 +10604,17 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>MIEMI130.pdf</t>
+          <t>MIEMI550.pdf</t>
         </is>
       </c>
       <c r="F238" t="n">
-        <v>1441</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MIEMI430P</t>
+          <t>MIEMI550I</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10635,17 +10634,17 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>MIEMI430P.pdf</t>
+          <t>MIEMI550I.pdf</t>
         </is>
       </c>
       <c r="F239" t="n">
-        <v>63</v>
+        <v>488</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MIEMI550</t>
+          <t>MIEMN570</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10665,17 +10664,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>MIEMI550.pdf</t>
+          <t>MIEMN570.pdf</t>
         </is>
       </c>
       <c r="F240" t="n">
-        <v>502</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MIEMI550I</t>
+          <t>MIEMN570I</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10695,17 +10694,17 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>MIEMI550I.pdf</t>
+          <t>MIEMN570I.pdf</t>
         </is>
       </c>
       <c r="F241" t="n">
-        <v>488</v>
+        <v>820</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MIEMN570</t>
+          <t>MIEMU520P</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10725,17 +10724,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>MIEMN570.pdf</t>
+          <t>MIEMU520P.pdf</t>
         </is>
       </c>
       <c r="F242" t="n">
-        <v>1038</v>
+        <v>756</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MIEMN570I</t>
+          <t>VSN</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10755,17 +10754,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>MIEMN570I.pdf</t>
+          <t>MNDT102I_D FR VSN-RP1r_hlsi.pdf</t>
         </is>
       </c>
       <c r="F243" t="n">
-        <v>820</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MIEMU520P</t>
+          <t>MNDT1310</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10785,17 +10784,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>MIEMU520P.pdf</t>
+          <t>MNDT1310.pdf</t>
         </is>
       </c>
       <c r="F244" t="n">
-        <v>756</v>
+        <v>310</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>VSN</t>
+          <t>MNDT1311</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10815,17 +10814,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>MNDT102I_D FR VSN-RP1r_hlsi.pdf</t>
+          <t>MNDT1311.pdf</t>
         </is>
       </c>
       <c r="F245" t="n">
-        <v>1268</v>
+        <v>312</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MNDT1310</t>
+          <t>ms1-2-4</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10845,17 +10844,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>MNDT1310.pdf</t>
+          <t>ms1-2-4.pdf</t>
         </is>
       </c>
       <c r="F246" t="n">
-        <v>310</v>
+        <v>572</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MNDT1311</t>
+          <t>MS8</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10875,22 +10874,22 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>MNDT1311.pdf</t>
+          <t>MS8.pdf</t>
         </is>
       </c>
       <c r="F247" t="n">
-        <v>312</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ms1-2-4</t>
+          <t>PSU User Manual_MLT LNG</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Manual usuario</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10905,17 +10904,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>ms1-2-4.pdf</t>
+          <t>PSU User Manual_MLT LNG.pdf</t>
         </is>
       </c>
       <c r="F248" t="n">
-        <v>572</v>
+        <v>3083</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MS8</t>
+          <t>RIF_08791_01 - AC1469_It-eng</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10935,22 +10934,22 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>MS8.pdf</t>
+          <t>RIF_08791_01 - AC1469_It-eng.pdf</t>
         </is>
       </c>
       <c r="F249" t="n">
-        <v>2114</v>
+        <v>21</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>PSU User Manual_MLT LNG</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Manual usuario</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10965,17 +10964,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>PSU User Manual_MLT LNG.pdf</t>
+          <t>Tg-Honeywell_Introduccion.pdf</t>
         </is>
       </c>
       <c r="F250" t="n">
-        <v>3083</v>
+        <v>471</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>RIF_08791_01 - AC1469_It-eng</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -10995,11 +10994,11 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>RIF_08791_01 - AC1469_It-eng.pdf</t>
+          <t>Tg-Honeywell_Tecnico.pdf</t>
         </is>
       </c>
       <c r="F251" t="n">
-        <v>21</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="252">
@@ -11025,17 +11024,17 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Tg-Honeywell_Introduccion.pdf</t>
+          <t>TG-Honeywell_Usuario.pdf</t>
         </is>
       </c>
       <c r="F252" t="n">
-        <v>471</v>
+        <v>866</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>VSN4</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -11045,7 +11044,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -11055,11 +11054,11 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Tg-Honeywell_Tecnico.pdf</t>
+          <t>VSN4-PLUS_ITA.pdf</t>
         </is>
       </c>
       <c r="F253" t="n">
-        <v>2271</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="254">
@@ -11070,7 +11069,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía troubleshooting</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -11080,46 +11079,46 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>privado</t>
+          <t>guias</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>TG-Honeywell_Usuario.pdf</t>
+          <t>Al cambiar-el-nombre-del-plano-a desaparecido-el-plano-y-los-equipos.pdf</t>
         </is>
       </c>
       <c r="F254" t="n">
-        <v>866</v>
+        <v>22</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>VSN4</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Guía troubleshooting</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>privado</t>
+          <t>guias</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>VSN4-PLUS_ITA.pdf</t>
+          <t>Averia-de-resistencia-de-baterias-en-central-DXc.pdf</t>
         </is>
       </c>
       <c r="F255" t="n">
-        <v>1684</v>
+        <v>3</v>
       </c>
     </row>
     <row r="256">
@@ -11145,17 +11144,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Al cambiar-el-nombre-del-plano-a desaparecido-el-plano-y-los-equipos.pdf</t>
+          <t>Como-configurar-correos-en-un-TG-HONEYWELL.pdf</t>
         </is>
       </c>
       <c r="F256" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -11175,17 +11174,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Averia-de-resistencia-de-baterias-en-central-DXc.pdf</t>
+          <t>Como-solucionar-la-incidencia-TABLE-IS-FULL-en-el-TG.pdf</t>
         </is>
       </c>
       <c r="F257" t="n">
-        <v>3</v>
+        <v>152</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>Como-solucionar-una-deriva-a-tierra</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11205,17 +11204,17 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Como-configurar-correos-en-un-TG-HONEYWELL.pdf</t>
+          <t>Como-solucionar-una-deriva-a-tierra.pdf</t>
         </is>
       </c>
       <c r="F258" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>Dispositivos</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11235,17 +11234,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Como-solucionar-la-incidencia-TABLE-IS-FULL-en-el-TG.pdf</t>
+          <t>Compatibilidad-detectores-de-monoxido-NCO10-NCO100-VSN-CO.pdf</t>
         </is>
       </c>
       <c r="F259" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Como-solucionar-una-deriva-a-tierra</t>
+          <t>Compatibilidad-entre-equipos-Notifier-y-Morley</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11265,17 +11264,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Como-solucionar-una-deriva-a-tierra.pdf</t>
+          <t>Compatibilidad-entre-equipos-Notifier-y-Morley.pdf</t>
         </is>
       </c>
       <c r="F260" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Dispositivos</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11295,17 +11294,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Compatibilidad-detectores-de-monoxido-NCO10-NCO100-VSN-CO.pdf</t>
+          <t>Con-que-Sistema-Operativo-es-compatible-el-programa-de-la-DXc-Connexion.pdf</t>
         </is>
       </c>
       <c r="F261" t="n">
-        <v>144</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Compatibilidad-entre-equipos-Notifier-y-Morley</t>
+          <t>ZX - DX</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11325,17 +11324,17 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Compatibilidad-entre-equipos-Notifier-y-Morley.pdf</t>
+          <t>Con-que-Sistema-Operativo-es-compatible-el-programa-de-la-ZX-y-DX.pdf</t>
         </is>
       </c>
       <c r="F262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>Módulos</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11355,17 +11354,17 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Con-que-Sistema-Operativo-es-compatible-el-programa-de-la-DXc-Connexion.pdf</t>
+          <t>Conexionado-del-modulo-M710-CZ-MI-DCZM.pdf</t>
         </is>
       </c>
       <c r="F263" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ZX - DX</t>
+          <t>Módulos</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -11385,11 +11384,11 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Con-que-Sistema-Operativo-es-compatible-el-programa-de-la-ZX-y-DX.pdf</t>
+          <t>Conexionado-del-modulo-M710-CZR-MI-DCZRM.pdf</t>
         </is>
       </c>
       <c r="F264" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
     </row>
     <row r="265">
@@ -11415,17 +11414,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Conexionado-del-modulo-M710-CZ-MI-DCZM.pdf</t>
+          <t>Conexionado-del-modulo-M710-MI-DMMI.pdf</t>
         </is>
       </c>
       <c r="F265" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Módulos</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -11445,17 +11444,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Conexionado-del-modulo-M710-CZR-MI-DCZRM.pdf</t>
+          <t>Configuracion-entrada-digital-de-la-central-NFS-Supra-VSN-Plus2-ESS-2Plus.pdf</t>
         </is>
       </c>
       <c r="F266" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Módulos</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -11475,17 +11474,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Conexionado-del-modulo-M710-MI-DMMI.pdf</t>
+          <t>DXC-Como-conectar-una-sirena-de-lazo.pdf</t>
         </is>
       </c>
       <c r="F267" t="n">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -11505,11 +11504,11 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Configuracion-entrada-digital-de-la-central-NFS-Supra-VSN-Plus2-ESS-2Plus.pdf</t>
+          <t>DXc-Conexion-Como-solucionar-la-averia-de-Estado-Inconsistente-Anulado.pdf</t>
         </is>
       </c>
       <c r="F268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -11535,11 +11534,11 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>DXC-Como-conectar-una-sirena-de-lazo.pdf</t>
+          <t>DXc-Configuracion-de-la-tarjeta-232-aislada-para-comunicarse-con-el-TG.pdf</t>
         </is>
       </c>
       <c r="F269" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="270">
@@ -11565,11 +11564,11 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>DXc-Conexion-Como-solucionar-la-averia-de-Estado-Inconsistente-Anulado.pdf</t>
+          <t>DXC-Connexion-Ajuste-contraste-display.pdf</t>
         </is>
       </c>
       <c r="F270" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="271">
@@ -11595,11 +11594,11 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>DXc-Configuracion-de-la-tarjeta-232-aislada-para-comunicarse-con-el-TG.pdf</t>
+          <t>DXC-Connexion-Averia-F-Alimentacion-externa.pdf</t>
         </is>
       </c>
       <c r="F271" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272">
@@ -11625,11 +11624,11 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Ajuste-contraste-display.pdf</t>
+          <t>DXC-Connexion-Averia-Nueva-F-Alimentacion-externa.pdf</t>
         </is>
       </c>
       <c r="F272" t="n">
-        <v>3</v>
+        <v>411</v>
       </c>
     </row>
     <row r="273">
@@ -11655,11 +11654,11 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Averia-F-Alimentacion-externa.pdf</t>
+          <t>DXC-Connexion-Como-programar-una-salida-de-averia-general.pdf</t>
         </is>
       </c>
       <c r="F273" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274">
@@ -11685,11 +11684,11 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Averia-Nueva-F-Alimentacion-externa.pdf</t>
+          <t>DXc-Connexion-Como-solucionar-la-averia-de-Ent-Placa-1-o-2.pdf</t>
         </is>
       </c>
       <c r="F274" t="n">
-        <v>411</v>
+        <v>3</v>
       </c>
     </row>
     <row r="275">
@@ -11715,11 +11714,11 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Como-programar-una-salida-de-averia-general.pdf</t>
+          <t>DXC-Connexion-Compatibilidad-de-programas-con-versiones.pdf</t>
         </is>
       </c>
       <c r="F275" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276">
@@ -11745,11 +11744,11 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>DXc-Connexion-Como-solucionar-la-averia-de-Ent-Placa-1-o-2.pdf</t>
+          <t>DXC-Connexion-Instalacion-y-configuracion-del-modulo-de-comunicacion-RS232.pdf</t>
         </is>
       </c>
       <c r="F276" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277">
@@ -11775,11 +11774,11 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Compatibilidad-de-programas-con-versiones.pdf</t>
+          <t>DXC-No-puedo-comunicar-con-la-central.pdf</t>
         </is>
       </c>
       <c r="F277" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="278">
@@ -11805,11 +11804,11 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>DXC-Connexion-Instalacion-y-configuracion-del-modulo-de-comunicacion-RS232.pdf</t>
+          <t>DXc-Opciones-de-disparo-de-programas-Matrices.pdf</t>
         </is>
       </c>
       <c r="F278" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="279">
@@ -11835,11 +11834,11 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>DXC-No-puedo-comunicar-con-la-central.pdf</t>
+          <t>DXC-Porque-al-activan-elementos-en-alarma-no-se-enciende-su-led.pdf</t>
         </is>
       </c>
       <c r="F279" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
@@ -11865,11 +11864,11 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>DXc-Opciones-de-disparo-de-programas-Matrices.pdf</t>
+          <t>DXC-Puedo-anular-la-clave-de-usuario-y-acceder-directamente-al-teclado.pdf</t>
         </is>
       </c>
       <c r="F280" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
@@ -11895,7 +11894,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>DXC-Porque-al-activan-elementos-en-alarma-no-se-enciende-su-led.pdf</t>
+          <t>DXC-puedo-cambiar-la-clave-de-nivel-3.pdf</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -11925,11 +11924,11 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>DXC-Puedo-anular-la-clave-de-usuario-y-acceder-directamente-al-teclado.pdf</t>
+          <t>DXC-Referencias-repuestos.pdf</t>
         </is>
       </c>
       <c r="F282" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="283">
@@ -11955,11 +11954,11 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>DXC-puedo-cambiar-la-clave-de-nivel-3.pdf</t>
+          <t>DXc-Tipos-Abreviaturas-de-equipos.pdf</t>
         </is>
       </c>
       <c r="F283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -11985,11 +11984,11 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>DXC-Referencias-repuestos.pdf</t>
+          <t>DXc-Tipos-de-accion-para-entradas.pdf</t>
         </is>
       </c>
       <c r="F284" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285">
@@ -12015,17 +12014,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>DXc-Tipos-Abreviaturas-de-equipos.pdf</t>
+          <t>DXc_Connexion Averia-de-resistencia-de-baterias.pdf</t>
         </is>
       </c>
       <c r="F285" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12045,11 +12044,11 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>DXc-Tipos-de-accion-para-entradas.pdf</t>
+          <t>ECO1000-CONEXIONADO-BASE-ECO1000.pdf</t>
         </is>
       </c>
       <c r="F286" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="287">
@@ -12075,7 +12074,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>DXc_Connexion Averia-de-resistencia-de-baterias.pdf</t>
+          <t>Eventos-Averias-de-Equipos-en-DXc.pdf</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -12085,7 +12084,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>FAAST-LT/8100E</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12105,17 +12104,17 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>ECO1000-CONEXIONADO-BASE-ECO1000.pdf</t>
+          <t>FAAST-LT-Como-comunicar-con-el-equipo.pdf</t>
         </is>
       </c>
       <c r="F288" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>FAAST-LT/8100E</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12135,11 +12134,11 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Eventos-Averias-de-Equipos-en-DXc.pdf</t>
+          <t>FAAST-LT-Como-obtener-el-historico-del-equipo.pdf</t>
         </is>
       </c>
       <c r="F289" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
     </row>
     <row r="290">
@@ -12165,17 +12164,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>FAAST-LT-Como-comunicar-con-el-equipo.pdf</t>
+          <t>FAAST-LT-No-puedo-comunicar-con-el-equipo.pdf</t>
         </is>
       </c>
       <c r="F290" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>FAAST-LT/8100E</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12195,17 +12194,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>FAAST-LT-Como-obtener-el-historico-del-equipo.pdf</t>
+          <t>Fallo-I2C-en-RP1rSupra.pdf</t>
         </is>
       </c>
       <c r="F291" t="n">
-        <v>109</v>
+        <v>2</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>FAAST-LT/8100E</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12225,17 +12224,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>FAAST-LT-No-puedo-comunicar-con-el-equipo.pdf</t>
+          <t>Finales-de-linea-de-las-centrales-convencionales.pdf</t>
         </is>
       </c>
       <c r="F292" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>Módulos</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12255,17 +12254,17 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Fallo-I2C-en-RP1rSupra.pdf</t>
+          <t>ITAC-Como-asignar-la-direccion-en-el-ITAC.pdf</t>
         </is>
       </c>
       <c r="F293" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>Módulos</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12285,17 +12284,17 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Finales-de-linea-de-las-centrales-convencionales.pdf</t>
+          <t>ITAC-no-reconocido-por-la-Central.pdf</t>
         </is>
       </c>
       <c r="F294" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Módulos</t>
+          <t>Vía Radio</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12315,17 +12314,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>ITAC-Como-asignar-la-direccion-en-el-ITAC.pdf</t>
+          <t>MIW-al-sustituir-las-baterias-de-un-equipo-se-necesita-programarlo-de-nuevo.pdf</t>
         </is>
       </c>
       <c r="F295" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Módulos</t>
+          <t>Vía Radio</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12345,11 +12344,11 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>ITAC-no-reconocido-por-la-Central.pdf</t>
+          <t>MIW-INT-Asignar-de-direccion-pasarela-detectores-y-Modulos-Via-radio-Morley.pdf</t>
         </is>
       </c>
       <c r="F296" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="297">
@@ -12375,11 +12374,11 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>MIW-al-sustituir-las-baterias-de-un-equipo-se-necesita-programarlo-de-nuevo.pdf</t>
+          <t>MIW-INT-Averia-de-TAMPER.pdf</t>
         </is>
       </c>
       <c r="F297" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="298">
@@ -12405,11 +12404,11 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>MIW-INT-Asignar-de-direccion-pasarela-detectores-y-Modulos-Via-radio-Morley.pdf</t>
+          <t>MIW-INT-Averias-baterias-pilas-via-radio-Morley.pdf</t>
         </is>
       </c>
       <c r="F298" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
     </row>
     <row r="299">
@@ -12435,11 +12434,11 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>MIW-INT-Averia-de-TAMPER.pdf</t>
+          <t>MIW-INT-Cable-para-comunicarse-con-interface-via-232.pdf</t>
         </is>
       </c>
       <c r="F299" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300">
@@ -12465,17 +12464,17 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>MIW-INT-Averias-baterias-pilas-via-radio-Morley.pdf</t>
+          <t>MIW-INT-Cuantos-expansores-puedo-conectar-al-Interface-pasarela.pdf</t>
         </is>
       </c>
       <c r="F300" t="n">
-        <v>134</v>
+        <v>49</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Vía Radio</t>
+          <t>MIW-INT</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12495,7 +12494,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>MIW-INT-Cable-para-comunicarse-con-interface-via-232.pdf</t>
+          <t>MIW-INT-Dar-de-alta-un-detector.pdf</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -12525,17 +12524,17 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>MIW-INT-Cuantos-expansores-puedo-conectar-al-Interface-pasarela.pdf</t>
+          <t>MIW-INT-Equipos-que-se-pueden-vincular-a-la-pasarela-interface-via-radio.pdf</t>
         </is>
       </c>
       <c r="F302" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MIW-INT</t>
+          <t>Vía Radio</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12555,7 +12554,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>MIW-INT-Dar-de-alta-un-detector.pdf</t>
+          <t>MIW-INT-La-central-DXC-indica-corto-tras-instalar-el-Interface.pdf</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -12585,7 +12584,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>MIW-INT-Equipos-que-se-pueden-vincular-a-la-pasarela-interface-via-radio.pdf</t>
+          <t>MIW-INT-La-central-indica-averia-de-datos-de-sensor.pdf</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -12595,7 +12594,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Vía Radio</t>
+          <t>MIW-INT</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -12615,11 +12614,11 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>MIW-INT-La-central-DXC-indica-corto-tras-instalar-el-Interface.pdf</t>
+          <t>MIW-INT-Mensaje-de-error-LOEr-via-radio-Morley.pdf</t>
         </is>
       </c>
       <c r="F305" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="306">
@@ -12645,7 +12644,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>MIW-INT-La-central-indica-averia-de-datos-de-sensor.pdf</t>
+          <t>MIW-INT-Programar-el-sistema-via-radio-sin-tenerlo-conectado-a-la-central.pdf</t>
         </is>
       </c>
       <c r="F306" t="n">
@@ -12655,7 +12654,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>MIW-INT</t>
+          <t>ZX - DX</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -12675,17 +12674,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>MIW-INT-Mensaje-de-error-LOEr-via-radio-Morley.pdf</t>
+          <t>Morley-Se-pueden-pasar-programaciones-de-ZX-y-Dimension-a-Connexion-DXC.pdf</t>
         </is>
       </c>
       <c r="F307" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Vía Radio</t>
+          <t>VSN2-PLUS</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -12705,17 +12704,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>MIW-INT-Programar-el-sistema-via-radio-sin-tenerlo-conectado-a-la-central.pdf</t>
+          <t>NFS-SUPRA-VISION-PLUS-2-Como-solucionar-el-Fallo-de-alimentacion.pdf</t>
         </is>
       </c>
       <c r="F308" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ZX - DX</t>
+          <t>VSN2-PLUS</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -12735,11 +12734,11 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Morley-Se-pueden-pasar-programaciones-de-ZX-y-Dimension-a-Connexion-DXC.pdf</t>
+          <t>NFS-SUPRA-VSN12-2PLUS-Funcionamiento-de-la-central-en-modo-prueba.pdf</t>
         </is>
       </c>
       <c r="F309" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="310">
@@ -12765,17 +12764,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>NFS-SUPRA-VISION-PLUS-2-Como-solucionar-el-Fallo-de-alimentacion.pdf</t>
+          <t>NFS-SUPRA-VSN2-PLUS-Entrada-Digital.pdf</t>
         </is>
       </c>
       <c r="F310" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>VSN2-PLUS</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -12795,17 +12794,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>NFS-SUPRA-VSN12-2PLUS-Funcionamiento-de-la-central-en-modo-prueba.pdf</t>
+          <t>Niveles-de-control-de-acceso-de-la-central-DXC-CONEXION.pdf</t>
         </is>
       </c>
       <c r="F311" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>VSN2-PLUS</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -12825,17 +12824,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>NFS-SUPRA-VSN2-PLUS-Entrada-Digital.pdf</t>
+          <t>No-aparecen-el-el-TG-ID3000-los-elementos-Auxiliares-AUX.pdf</t>
         </is>
       </c>
       <c r="F312" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>VSN2-PLUS</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -12855,17 +12854,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Niveles-de-control-de-acceso-de-la-central-DXC-CONEXION.pdf</t>
+          <t>No-funcionan-las-teclas-de-la-central-VSN.pdf</t>
         </is>
       </c>
       <c r="F313" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>ZX - DX</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -12885,17 +12884,17 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>No-aparecen-el-el-TG-ID3000-los-elementos-Auxiliares-AUX.pdf</t>
+          <t>No-puedo-conectarme-con-el-ordenador-a-la-central-ZX.pdf</t>
         </is>
       </c>
       <c r="F314" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>VSN2-PLUS</t>
+          <t>VSN-LT</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12915,17 +12914,17 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>No-funcionan-las-teclas-de-la-central-VSN.pdf</t>
+          <t>No-puedo-hacer-Rearme-o-silenciar-sirenas-en-la-VSN-LT.pdf</t>
         </is>
       </c>
       <c r="F315" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ZX - DX</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12945,17 +12944,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>No-puedo-conectarme-con-el-ordenador-a-la-central-ZX.pdf</t>
+          <t>No-puedo-hacer-rearmes-silenciar-sirenas-y-otros-controles-desde-el-TG-hacia.pdf</t>
         </is>
       </c>
       <c r="F316" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>VSN-LT</t>
+          <t>Módulos</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12975,11 +12974,11 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>No-puedo-hacer-Rearme-o-silenciar-sirenas-en-la-VSN-LT.pdf</t>
+          <t>OSID-Es-necesario-resetear-la-barrera-de-forma-externa.pdf</t>
         </is>
       </c>
       <c r="F317" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -13005,17 +13004,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>No-puedo-hacer-rearmes-silenciar-sirenas-y-otros-controles-desde-el-TG-hacia.pdf</t>
+          <t>Poner-la-contraseña-por-defecto-del-programa-de-gestion-grafica-TG.pdf</t>
         </is>
       </c>
       <c r="F318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Módulos</t>
+          <t>ZX - DX</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -13035,17 +13034,17 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>OSID-Es-necesario-resetear-la-barrera-de-forma-externa.pdf</t>
+          <t>Puesta-en-marcha-repetidor-ZXrA-en-central-CONNEXION.pdf</t>
         </is>
       </c>
       <c r="F319" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>DXc- Connexion</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -13065,17 +13064,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Poner-la-contraseña-por-defecto-del-programa-de-gestion-grafica-TG.pdf</t>
+          <t>Rearme-remoto-en-central-DXc-Connexion.pdf</t>
         </is>
       </c>
       <c r="F320" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ZX - DX</t>
+          <t>Relacion-de-producto-obsoleto-de-Morley-IAS-by-Hon</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -13095,17 +13094,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Puesta-en-marcha-repetidor-ZXrA-en-central-CONNEXION.pdf</t>
+          <t>Relacion-de-producto-obsoleto-de-Morley-IAS-by-Honeywell.pdf</t>
         </is>
       </c>
       <c r="F321" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>DXc- Connexion</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -13125,17 +13124,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Rearme-remoto-en-central-DXc-Connexion.pdf</t>
+          <t>Requisitos-del-PC-para-el-TG-Version-5-XX.pdf</t>
         </is>
       </c>
       <c r="F322" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Relacion-de-producto-obsoleto-de-Morley-IAS-by-Hon</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -13155,17 +13154,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Relacion-de-producto-obsoleto-de-Morley-IAS-by-Honeywell.pdf</t>
+          <t>RP1r-Supra-VSN-RP1R-PLUS2-Como-cambiar-el-tipo-de-final-del-linea.pdf</t>
         </is>
       </c>
       <c r="F323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>VSN-Plus2</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -13185,11 +13184,11 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Requisitos-del-PC-para-el-TG-Version-5-XX.pdf</t>
+          <t>RP1R-SUPRA-VSN-RP1R-PLUS2-Teclado-bloqueado.pdf</t>
         </is>
       </c>
       <c r="F324" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
@@ -13215,17 +13214,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>RP1r-Supra-VSN-RP1R-PLUS2-Como-cambiar-el-tipo-de-final-del-linea.pdf</t>
+          <t>RP1r-Supra-VSNRP1r-2Plus-Sirena-sin-sonido-pulsante.pdf</t>
         </is>
       </c>
       <c r="F325" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>VSN-Plus2</t>
+          <t>VSN-RP1R</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13245,17 +13244,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>RP1R-SUPRA-VSN-RP1R-PLUS2-Teclado-bloqueado.pdf</t>
+          <t>RP1R-Supra_VSN-RP1R-PLUS2-Averia-Rl_y_Fallo-de-sistema-intermitente.pdf</t>
         </is>
       </c>
       <c r="F326" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13275,17 +13274,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>RP1r-Supra-VSNRP1r-2Plus-Sirena-sin-sonido-pulsante.pdf</t>
+          <t>TG-ATENCION-El-sistema-no-encuentra-la-proteccion-del-TG.pdf</t>
         </is>
       </c>
       <c r="F327" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>VSN-RP1R</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -13305,17 +13304,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>RP1R-Supra_VSN-RP1R-PLUS2-Averia-Rl_y_Fallo-de-sistema-intermitente.pdf</t>
+          <t>TG-Como ampliar-licencias.pdf</t>
         </is>
       </c>
       <c r="F328" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Solicitud-asistencia-curso-de-formacion-puesta-en-</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13335,7 +13334,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Solicitud-asistencia-curso-de-formacion-puesta-en-marcha-consultas-tecnica.pdf</t>
+          <t>TG-Como-borrar-elementos-de-un-plano.pdf</t>
         </is>
       </c>
       <c r="F329" t="n">
@@ -13365,11 +13364,11 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>TG-ATENCION-El-sistema-no-encuentra-la-proteccion-del-TG.pdf</t>
+          <t>TG-Como-cargar-añadir-planos.pdf</t>
         </is>
       </c>
       <c r="F330" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="331">
@@ -13395,7 +13394,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>TG-Como ampliar-licencias.pdf</t>
+          <t>TG-Como-exportar-el-historico-desde-el-programa-de-gestion-grafica.pdf</t>
         </is>
       </c>
       <c r="F331" t="n">
@@ -13425,7 +13424,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>TG-Como-borrar-elementos-de-un-plano.pdf</t>
+          <t>TG-Como-hacer-una-copia-de-seguridad-del-proyecto.pdf</t>
         </is>
       </c>
       <c r="F332" t="n">
@@ -13455,11 +13454,11 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>TG-Como-cargar-añadir-planos.pdf</t>
+          <t>TG-Como-puedo-ver-los-equipos-que-no-estan-representados-en-planos.pdf</t>
         </is>
       </c>
       <c r="F333" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
     </row>
     <row r="334">
@@ -13485,11 +13484,11 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>TG-Como-exportar-el-historico-desde-el-programa-de-gestion-grafica.pdf</t>
+          <t>TG-Como-reparar-Historico-Provisional.pdf</t>
         </is>
       </c>
       <c r="F334" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="335">
@@ -13515,7 +13514,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>TG-Como-hacer-una-copia-de-seguridad-del-proyecto.pdf</t>
+          <t>TG-como-se-configuran-sonidos-ante-eventos.pdf</t>
         </is>
       </c>
       <c r="F335" t="n">
@@ -13545,7 +13544,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>TG-Como-puedo-ver-los-equipos-que-no-estan-representados-en-planos.pdf</t>
+          <t>TG-Como-solucionar-problema-de-Error-CRC.pdf</t>
         </is>
       </c>
       <c r="F336" t="n">
@@ -13575,11 +13574,11 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>TG-Como-reparar-Historico-Provisional.pdf</t>
+          <t>TG-Cuales-son-los-requisitos-del-PC-para-el-programa.pdf</t>
         </is>
       </c>
       <c r="F337" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="338">
@@ -13605,17 +13604,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>TG-como-se-configuran-sonidos-ante-eventos.pdf</t>
+          <t>TG-GSM-Fallo-al-enviar-SMS-desde-TG.pdf</t>
         </is>
       </c>
       <c r="F338" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>TG-IP1-SEC</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -13635,17 +13634,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>TG-Como-solucionar-problema-de-Error-CRC.pdf</t>
+          <t>TG-IP-1-SEC-Que-direccion-IP-tiene-por-defecto.pdf</t>
         </is>
       </c>
       <c r="F339" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>TG-IP1-SEC</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -13665,11 +13664,11 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>TG-Cuales-son-los-requisitos-del-PC-para-el-programa.pdf</t>
+          <t>TG-IP1-SEC-Como-volver-a-fabrica-el-dispositivo.pdf</t>
         </is>
       </c>
       <c r="F340" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="341">
@@ -13695,7 +13694,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>TG-GSM-Fallo-al-enviar-SMS-desde-TG.pdf</t>
+          <t>TG-Que-clave-tiene-si-se-instala-en-idioma-Ingles.pdf</t>
         </is>
       </c>
       <c r="F341" t="n">
@@ -13705,7 +13704,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TG-IP1-SEC</t>
+          <t>TG</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13725,17 +13724,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>TG-IP-1-SEC-Que-direccion-IP-tiene-por-defecto.pdf</t>
+          <t>TG-SE-HA-SUPERADO-EL-MAXIMO-DE-LICENCIAS.pdf</t>
         </is>
       </c>
       <c r="F342" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>TG-IP1-SEC</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13755,17 +13754,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>TG-IP1-SEC-Como-volver-a-fabrica-el-dispositivo.pdf</t>
+          <t>UCIP-Acceso-a-comandos-AT-para-chequeo.pdf</t>
         </is>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13785,7 +13784,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>TG-Que-clave-tiene-si-se-instala-en-idioma-Ingles.pdf</t>
+          <t>UCIP-Borrado-a-valores-de-fabrica.pdf</t>
         </is>
       </c>
       <c r="F344" t="n">
@@ -13795,7 +13794,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TG</t>
+          <t>UCIP</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13815,7 +13814,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>TG-SE-HA-SUPERADO-EL-MAXIMO-DE-LICENCIAS.pdf</t>
+          <t>UCIP-Borrar-configuracion-completa.pdf</t>
         </is>
       </c>
       <c r="F345" t="n">
@@ -13845,7 +13844,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>UCIP-Acceso-a-comandos-AT-para-chequeo.pdf</t>
+          <t>UCIP-Borrar-datos-de-CRA1-o-2.pdf</t>
         </is>
       </c>
       <c r="F346" t="n">
@@ -13875,11 +13874,11 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>UCIP-Borrado-a-valores-de-fabrica.pdf</t>
+          <t>UCIP-Cambio-de-puerto-TCP-en-GPRS.pdf</t>
         </is>
       </c>
       <c r="F347" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -13905,7 +13904,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>UCIP-Borrar-configuracion-completa.pdf</t>
+          <t>UCIP-Cambio-de-puerto-TCP-red-LAN.pdf</t>
         </is>
       </c>
       <c r="F348" t="n">
@@ -13935,7 +13934,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>UCIP-Borrar-datos-de-CRA1-o-2.pdf</t>
+          <t>UCIP-Como hacer una Actualizacion.pdf</t>
         </is>
       </c>
       <c r="F349" t="n">
@@ -13965,7 +13964,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>UCIP-Cambio-de-puerto-TCP-en-GPRS.pdf</t>
+          <t>UCIP-Como-conectar-con-TG.pdf</t>
         </is>
       </c>
       <c r="F350" t="n">
@@ -13995,11 +13994,11 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>UCIP-Cambio-de-puerto-TCP-red-LAN.pdf</t>
+          <t>UCIP-Como-configurar-envio-de-eventos-por-equipo.pdf</t>
         </is>
       </c>
       <c r="F351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -14025,7 +14024,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>UCIP-Como hacer una Actualizacion.pdf</t>
+          <t>UCIP-Como-enviar-datos-de-equipos-y-no-solo-eventos-de-zonas.pdf</t>
         </is>
       </c>
       <c r="F352" t="n">
@@ -14055,11 +14054,11 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>UCIP-Como-conectar-con-TG.pdf</t>
+          <t>UCIP-Compatibilidades-con-centrales-actuales.pdf</t>
         </is>
       </c>
       <c r="F353" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="354">
@@ -14085,11 +14084,11 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>UCIP-Como-configurar-envio-de-eventos-por-equipo.pdf</t>
+          <t>UCIP-Conectar-con-equipo-via-IP.pdf</t>
         </is>
       </c>
       <c r="F354" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="355">
@@ -14115,11 +14114,11 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>UCIP-Como-enviar-datos-de-equipos-y-no-solo-eventos-de-zonas.pdf</t>
+          <t>UCIP-Conectar-con-equipo-via-Serie.pdf</t>
         </is>
       </c>
       <c r="F355" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="356">
@@ -14145,11 +14144,11 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>UCIP-Compatibilidades-con-centrales-actuales.pdf</t>
+          <t>UCIP-Conectar-con-VSN2plus.pdf</t>
         </is>
       </c>
       <c r="F356" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="357">
@@ -14175,11 +14174,11 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>UCIP-Conectar-con-equipo-via-IP.pdf</t>
+          <t>UCIP-Conexionado-con-ID3000.pdf</t>
         </is>
       </c>
       <c r="F357" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
@@ -14205,11 +14204,11 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>UCIP-Conectar-con-equipo-via-Serie.pdf</t>
+          <t>UCIP-Configuracion-CRA1.pdf</t>
         </is>
       </c>
       <c r="F358" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359">
@@ -14235,7 +14234,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>UCIP-Conectar-con-VSN2plus.pdf</t>
+          <t>UCIP-Configurar-envio-de-SMS.pdf</t>
         </is>
       </c>
       <c r="F359" t="n">
@@ -14265,7 +14264,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>UCIP-Conexionado-con-ID3000.pdf</t>
+          <t>UCIP-Configurar-PIN-tarjeta-SIM.pdf</t>
         </is>
       </c>
       <c r="F360" t="n">
@@ -14295,11 +14294,11 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>UCIP-Configuracion-CRA1.pdf</t>
+          <t>UCIP-Configurar-puerto-UART-de-UCIP.pdf</t>
         </is>
       </c>
       <c r="F361" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -14325,7 +14324,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>UCIP-Configurar-envio-de-SMS.pdf</t>
+          <t>UCIP-No-conecta-por-IP.pdf</t>
         </is>
       </c>
       <c r="F362" t="n">
@@ -14355,7 +14354,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>UCIP-Configurar-PIN-tarjeta-SIM.pdf</t>
+          <t>UCIP-Programacion-IP-de-equipo.pdf</t>
         </is>
       </c>
       <c r="F363" t="n">
@@ -14385,11 +14384,11 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>UCIP-Configurar-puerto-UART-de-UCIP.pdf</t>
+          <t>UCIP-Que-datos-necesito-de-la-receptora.pdf</t>
         </is>
       </c>
       <c r="F364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
@@ -14415,11 +14414,11 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>UCIP-No-conecta-por-IP.pdf</t>
+          <t>UCIP-Tabla-de-compatibilidad-con-receptoras-y-centrales.pdf</t>
         </is>
       </c>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="366">
@@ -14445,11 +14444,11 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>UCIP-Programacion-IP-de-equipo.pdf</t>
+          <t>UCIP-Ver-configuracion-de-equipo.pdf</t>
         </is>
       </c>
       <c r="F366" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="367">
@@ -14475,17 +14474,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>UCIP-Que-datos-necesito-de-la-receptora.pdf</t>
+          <t>UCIP-Verificar-cobertura-GSM.pdf</t>
         </is>
       </c>
       <c r="F367" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>VSN-Plus2</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14505,17 +14504,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>UCIP-Tabla-de-compatibilidad-con-receptoras-y-centrales.pdf</t>
+          <t>Ver-Como-Cambiar-configuracion-de-las-Funciones-especiales-en-las-centrales-.pdf</t>
         </is>
       </c>
       <c r="F368" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>Dispositivos</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14535,17 +14534,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>UCIP-Ver-configuracion-de-equipo.pdf</t>
+          <t>VSN-CO-Mantenimiento-y-vida-util-del-detector.pdf</t>
         </is>
       </c>
       <c r="F369" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>UCIP</t>
+          <t>VSN2-PLUS</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14565,100 +14564,10 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>UCIP-Verificar-cobertura-GSM.pdf</t>
+          <t>VSN-CRA-Centrales-compatibles.pdf</t>
         </is>
       </c>
       <c r="F370" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>VSN-Plus2</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>Guía troubleshooting</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>guias</t>
-        </is>
-      </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>Ver-Como-Cambiar-configuracion-de-las-Funciones-especiales-en-las-centrales-.pdf</t>
-        </is>
-      </c>
-      <c r="F371" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Dispositivos</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>Guía troubleshooting</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>guias</t>
-        </is>
-      </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>VSN-CO-Mantenimiento-y-vida-util-del-detector.pdf</t>
-        </is>
-      </c>
-      <c r="F372" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>VSN2-PLUS</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>Guía troubleshooting</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>guias</t>
-        </is>
-      </c>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t>VSN-CRA-Centrales-compatibles.pdf</t>
-        </is>
-      </c>
-      <c r="F373" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/Inventario_Manuales.xlsx
+++ b/data/Inventario_Manuales.xlsx
@@ -11,10 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detnov" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Morley" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notifier" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kidde" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aritech" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edwards" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otros" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aritech" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edwards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Otros" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kidde" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="C11" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -34436,1710 +34436,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="B1" s="18" t="inlineStr">
-        <is>
-          <t>Tipo documento</t>
-        </is>
-      </c>
-      <c r="C1" s="18" t="inlineStr">
-        <is>
-          <t>Idioma</t>
-        </is>
-      </c>
-      <c r="D1" s="18" t="inlineStr">
-        <is>
-          <t>Subcarpeta</t>
-        </is>
-      </c>
-      <c r="E1" s="18" t="inlineStr">
-        <is>
-          <t>Archivo</t>
-        </is>
-      </c>
-      <c r="F1" s="18" t="inlineStr">
-        <is>
-          <t>Tamaño (KB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>00-3280-501-4003-05_r005_2x-a_series_installation_manual_en_0.pdf</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>4810</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2X-A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>00-3280-501-4009-05_r005_2x-a_series_installation_manual_es.pdf</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>5001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2X-A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Manual usuario</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>00-3280-505-4009-04_r004_2x-a_series_operation_manual_es.pdf</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>00-3280-507-4003-03_r003_2x-a_series_quick_installation_guide_en.pdf</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2X-A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>00-3280-507-4009-03_r003_2x-a_series_quick_installation_guide_es.pdf</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2X-A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>00-3280-508-4009-03_r003_2x-a_series_quick_operation_guide_es.pdf</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>00-3280-508-4109-06_r006_2x-at_series_quick_start_guide_es.pdf</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>00-3280-508-4209-02_r002_2x-at_series_quick_operation_guide_es.pdf</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KE-DM3010R-KIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>03-0210-501-4300-06_r006_excellence_series_addressable_mcp_installation_sheet_ml.pdf</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2X-AF1-S</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2x-af1-s-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2X-AF2-FB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2x-af2-fb-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2X-AF2-FB-S</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2x-af2-fb-s-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2X-AF2-SCFB</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2x-af2-scfb-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2X-AF2-SCFB-S</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2x-af2-scfb-s-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2X-AT-F2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2x-at-f2-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2X-AT-F2-FB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2x-at-f2-fb-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2X-AT-F2-FB-P</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2x-at-f2-fb-p-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2X-AT-F2-FB-S</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2x-at-f2-fb-s-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2X-AT-F2-P</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2x-at-f2-p-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2X-AT-F2-S</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2x-at-f2-s-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KE-DP3020W</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>3102984-ml_r003_excellence_series_intelligent_addressable_dual_optical_detector_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KE-DT3001W-HAB</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>3102986-ml_r002_excellence_series_intelligent_addressable_class_a-b_heat_detector_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KE-DB3010W</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>3102987-ml_r003_excellence_series_standard_mounting_base_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>KE-DBA-AUXW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>3103013-ml_r002_ke-dba-auxw_deep_accessory_for_standard_mounting_base_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>KE-IO3101</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>3103062-ml_r003_excellence_series_addressable_single_output_module_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>KE-IO3122</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>3103063-ml_r003_excellence_series_addressable_two-four_input-output_module_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>KE-AS3115R-WM</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>3103072-ml_r004_excellence_series_intelligent_addressable_indoor_notification_device_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>3036</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>9-30781-KID-EN</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>3103092-es_r003_modulaser_en_54-20_installation_manual_kidde_0.pdf</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>6029</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>KE-AS3115R-WMIP</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>3103198-ml_r002_excellence_series_intelligent_addressable_outdoor_notification_device_installation_sheet.pdf</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>3366</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Manual técnico</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>3103267-en_r001_2x-a_series_kuwait_marketplace_manual.pdf</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>9-30781-KID-EN</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>9-30781-kid-en-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>9-30783-KID-EN</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>9-30783-kid-en-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Manual instalación</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>bcn-3100017-es_r002_nc_series_fire_alarm_control_panel_installation_manual.pdf</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>3723</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Manual usuario</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>bcn-3100018-es_r002_nc_series_fire_alarm_control_panel_operation_manual.pdf</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>bcn-3100019-es_r002_nc_series_fire_alarm_control_panel_quick_installation_guide.pdf</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Guía rápida</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>bcn-3100020-es_r002_nc_series_fire_alarm_control_panel_quick_operation_guide.pdf</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Manual técnico</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>bcn-3100035-en_r006_2x-a_series_addressable_control_panel_compatibility_list_0.pdf</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2X-A Táctil</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Manual técnico</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>bcn-3100036-en_r002_2x-a_and_zp2-a_series_addressable_control_panel_compatibility_list_900_series_protocol.pdf</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>KE-AS3115R-WM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>ke-as3115r-wm-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1104</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>KE-AS3115R-WMIP</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>ke-as3115r-wmip-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>KE-DB3010W</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ke-db3010w-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>1441</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>KE-DBA-AUXW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>ke-dba-auxw-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>KE-DM3010R</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ke-dm3010r-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>KE-DM3010R-KIT</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>ke-dm3010r-kit-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KE-DP3020W</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>ke-dp3020w-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>KE-DP3120W</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>ke-dp3120w-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KE-DT3001W-HAB</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ke-dt3001w-hab-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>KE-IO3101</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>ke-io3101-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KE-IO3122</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ke-io3122-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>KE-IO3144</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ke-io3144-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NC-PF2</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>nc-pf2-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NC-PF4</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>nc-pf4-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NC-PF4-SC</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>nc-pf4-sc-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NC-PF8</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>nc-pf8-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NC-PF8-SC</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Datasheet</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>portal</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>nc-pf8-sc-161721-es.pdf</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>617</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -37178,7 +35474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37322,7 +35618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -37854,4 +36150,3928 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F130"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Producto</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Tipo documento</t>
+        </is>
+      </c>
+      <c r="C1" s="18" t="inlineStr">
+        <is>
+          <t>Idioma</t>
+        </is>
+      </c>
+      <c r="D1" s="18" t="inlineStr">
+        <is>
+          <t>Subcarpeta</t>
+        </is>
+      </c>
+      <c r="E1" s="18" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Tamaño (KB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>00-3280-501-4003-05_r005_2x-a_series_installation_manual_en_0.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4810</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2X-A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>00-3280-501-4009-05_r005_2x-a_series_installation_manual_es.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>5001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2X-A</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>00-3280-505-4009-04_r004_2x-a_series_operation_manual_es.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>00-3280-507-4003-03_r003_2x-a_series_quick_installation_guide_en.pdf</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2X-A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>00-3280-507-4009-03_r003_2x-a_series_quick_installation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2X-A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>00-3280-508-4009-03_r003_2x-a_series_quick_operation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>00-3280-508-4109-06_r006_2x-at_series_quick_start_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>00-3280-508-4209-02_r002_2x-at_series_quick_operation_guide_es.pdf</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KE-DM3010R-KIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>03-0210-501-4300-06_r006_excellence_series_addressable_mcp_installation_sheet_ml.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2X-AF1-S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2x-af1-s-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2X-AF2-FB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2x-af2-fb-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2X-AF2-FB-S</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2x-af2-fb-s-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2X-AF2-SCFB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2x-af2-scfb-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2X-AF2-SCFB-S</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2x-af2-scfb-s-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2X-AT-F2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2x-at-f2-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2X-AT-F2-FB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2x-at-f2-fb-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2X-AT-F2-FB-P</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2x-at-f2-fb-p-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2X-AT-F2-FB-S</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2x-at-f2-fb-s-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2X-AT-F2-P</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2x-at-f2-p-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2X-AT-F2-S</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2x-at-f2-s-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KE-DP3020W</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3102984-ml_r003_excellence_series_intelligent_addressable_dual_optical_detector_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KE-DT3001W-HAB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3102986-ml_r002_excellence_series_intelligent_addressable_class_a-b_heat_detector_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KE-DB3010W</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3102987-ml_r003_excellence_series_standard_mounting_base_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KE-DBA-AUXW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>3103013-ml_r002_ke-dba-auxw_deep_accessory_for_standard_mounting_base_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>KE-IO3101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>3103062-ml_r003_excellence_series_addressable_single_output_module_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KE-IO3122</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>3103063-ml_r003_excellence_series_addressable_two-four_input-output_module_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WM</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3103072-ml_r004_excellence_series_intelligent_addressable_indoor_notification_device_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>9-30781-KID-EN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3103092-es_r003_modulaser_en_54-20_installation_manual_kidde_0.pdf</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>6029</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WMIP</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3103198-ml_r002_excellence_series_intelligent_addressable_outdoor_notification_device_installation_sheet.pdf</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3366</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3103267-en_r001_2x-a_series_kuwait_marketplace_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>9-30781-KID-EN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>9-30781-kid-en-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>9-30783-KID-EN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>9-30783-kid-en-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>bcn-3100017-es_r002_nc_series_fire_alarm_control_panel_installation_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3723</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>bcn-3100018-es_r002_nc_series_fire_alarm_control_panel_operation_manual.pdf</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>bcn-3100019-es_r002_nc_series_fire_alarm_control_panel_quick_installation_guide.pdf</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bcn-3100020-es_r002_nc_series_fire_alarm_control_panel_quick_operation_guide.pdf</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bcn-3100035-en_r006_2x-a_series_addressable_control_panel_compatibility_list_0.pdf</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2X-A Táctil</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Manual técnico</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bcn-3100036-en_r002_2x-a_and_zp2-a_series_addressable_control_panel_compatibility_list_900_series_protocol.pdf</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2A-PAK-HPL</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_2A_PAK_HPL_9085.pdf</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2X-AT-FR-FB-S</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_2X_AT_FR_FB_S_202602_ES_4276.pdf</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2X-AT-FR-S</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_2X_AT_FR_S_202602_ES_904a.pdf</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2X-AT-FR-S</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_2X_AT_FR_S_98dc.pdf</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KE-AS3005W-WM</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3005W_WM_2602_ES_88a2.pdf</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KE-AS3010R</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3010R_2602_161a.pdf</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>KE-AS3010R/KE-AS3010R-IP</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3010R_IP_2602_ING_a4e2.pdf</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KE-AS3010W</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3010W_2602_ES_3217.pdf</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KE-AS3011R</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3011R_2602_ES_3a29.pdf</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>KE-AS3011R/KE-AS3011R-IP</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3011R_IP_2602_ING_9304.pdf</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KE-AS3011W</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3011W_2602_ES_fb30.pdf</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KE-AS3015R-WM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3015R_WM_2602_ES_5cb3.pdf</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>KE-AS3015R-WM/KE-AS3015R-WMIP</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3015R_WMIP_2602_ING_92b3.pdf</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>KE-AS3015W-WM/KE-AS3105W-WM</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3015W_WM_2602_ES_8142.pdf</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>KE-AS3105W-WM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3105W_WM_2602_ES_7bbc.pdf</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>KE-AS3110R</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3110R_2602_ES_7e88.pdf</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>KE-AS3110R/KE-AS3110R-IP</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3110R_IP_2602_ING_5e66.pdf</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>KE-AS3110W</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3110W_2602_ES_75f3.pdf</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KE-AS3111R</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3111R_2602_ES_8dce.pdf</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>KE-AS3111R/KE-AS3111R-IP</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3111R_IP_2602_ING_72bd.pdf</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KE-AS3111W</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3111W_2602_ES_027c.pdf</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>KE-AS3115W-WM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_AS3115W_WM_2602_ES_488d.pdf</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>KE-ASA-AUXR</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_ASA_AUXR_f28f.pdf</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>KE-DBA-ADPW-KIL</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DBA_ADPW_KIL_202501_ING_c855.pdf</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>KE-DBA-ADPW-ZIT</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DBA_ADPW_ZIT_202501_ING_ed63.pdf</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>KE-DM3110R-IP</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DM3110R_IP_202412_ES_8165.pdf</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>KE-DM3110R-KIT</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DM3110R_KIT_f3b7.pdf</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>KE-DP3121B/KE-DP3121B-SNV</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DP3121B_SNV_202503_ES_b5bc.pdf</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>KE-DP3121W/KE-DP3121W-SN</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DP3121W_SN_202503_ES_5938.pdf</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>KE-DP3121W/KE-DP3121W-SN/KE-DP3121W-SNV</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_DP3121W_SNV_202503_ES_8699.pdf</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>KE-IU3111-ZME/KIT 2X-AE1-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KE_IU3111_ZME_f908.pdf</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>KIT 2X-AFR-C-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_KIT_2X_AFR_C_09_202412_ES_c976.pdf</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>N-IO-MBX-1/N-IO-MBX-2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_N_IO_MBX_1_202505_ES_07ca.pdf</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>N-IO-MBX-2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_N_IO_MBX_2_202505_ES_b34f.pdf</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>N-IO-SBX-1G/N-IO-SBX-2G</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_N_IO_SBX_1G_202505_ES_b086.pdf</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>N-IO-SBX-2G</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_N_IO_SBX_2G_202505_ES_6eb1.pdf</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ZLSM-MD</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_ZLSM_MD_202604_ES_8d42.pdf</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ZLSM-ME/ZLSM-MR</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_ZLSM_ME_202604_ES_c3d9.pdf</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ZLSM-MR</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>DS_KIDDE_ZLSM_MR_202604_ES_6a09.pdf</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KE-DBA-ADPW-KIL/KE-DBA-ADPW-ZIT</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Guía instalación</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>G_INST_KIDDE_KE_DBA_ADPW_202502_ES_70e7.pdf</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>3155</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>NC-PF2/NC-PF4/NC-PF8/NC-PF2-SC/NC-PF4-SC/NC-PF8-SC</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Guía instalación</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>G_INST_KIDDE_NC_PFx_202502_ES_ac3d.pdf</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>NC-PF2/NC-PF4/NC-PF8/NC-PF2-SC/NC-PF4-SC/NC-PF8-SC</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Guía uso</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>G_USO_KIDDE_NC_PFx_202502_ES_99d2.pdf</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2X-AT-FR-FB-S/2X-AT-FR-S</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>GR_KIDDE_2X_AT_FR_FB_S_27cf.pdf</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>KE-DB3010B</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>HD_KE_DB3010B_202407_ES_1065.pdf</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>KE-DBA-CAPW</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_CAPW_202407_ING_d87d.pdf</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>KE-DBA-IPW</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_IPW_202407_ING_ffaf.pdf</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>KE-DBA-LABW-L1S/KE-DBA-LABW-L2S/KE-DBA-LABW-L3S/KE-DBA-LABW-L4S</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_LABW_LxS_202407_ES_2fc1.pdf</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>KE-DBA-RECW</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_RECW_202407_ES_bb2b.pdf</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>KE-DBA-SKTW</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_SKTW_202407_ING_2da9.pdf</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>KE-DBA-TAGW</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>HD_KE_DBA_TAGW_202407_ES_4b26.pdf</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>KE-DP3021B</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>HD_KE_DP3021B_202407_ES_861a.pdf</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>KE-DP3021W</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>HD_KE_DP3021W_202407_ES_778e.pdf</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>KE-DP3121B</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>HD_KE_DP3121B_202407_ES_8c51.pdf</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>KE-DT3101W-HAB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>HD_KE_DT3101W_HAB_202407_ES_30e0.pdf</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>KE-IU3110</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>HD_KE_IU3110_202407_ES_42d6.pdf</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NC-PF2/NC-PF4/NC-PF8/NC-PF2-SC/NC-PF4-SC/NC-PF8-SC</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Guía rápida</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>INC___DOCI_141_Gu__a_r__pida_Kidde_NC_PF__1__fcb9.pdf</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WM</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>ke-as3115r-wm-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KE-AS3115R-WMIP</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ke-as3115r-wmip-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KE-DB3010W</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ke-db3010w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>KE-DBA-AUXW</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ke-dba-auxw-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>KE-DM3010R</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>ke-dm3010r-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>KE-DM3010R-KIT</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ke-dm3010r-kit-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>KE-DP3020W</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>ke-dp3020w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>KE-DP3120W</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>ke-dp3120w-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>KE-DT3001W-HAB</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>ke-dt3001w-hab-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>KE-IO3101</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>ke-io3101-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KE-IO3122</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>ke-io3122-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>KE-IO3144</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ke-io3144-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KE-DBA-IPW</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MI_KE_DBA_IPW_202407_ES_cc56.pdf</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>KE-DBA-RECW</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MI_KE_DBA_RECW_202407_ES_aacc.pdf</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>KE-DBA-SKTW</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MI_KE_DBA_SKTW_202407_ES_a20b.pdf</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>KE-IU3110</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>MI_KE_IU3110_202407_ES_5e36.pdf</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>KE-IU3111-ZME/KIT 2X-AE1-09</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>MI_KE_IU3111_ZME_202407_ES_fde1.pdf</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1326</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2A-PAK-HPL</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_2A_PAK_HPL_c599.pdf</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2X-AT-F2/2X-AT-F2-FB/2X-AT-FR-FB-S/2X-AT-FR-S</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_2X_AT_F2_FB_07d4.pdf</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>5842</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KE-AS3005W-WM/KE-AS3010R/KE-AS3010R-IP/KE-AS3010W/KE-AS3011R/KE-AS3015R-WM/KE-AS3015W-WM/KE-AS3105W-WM/KE-AS3110R/KE-AS3110W/KE-AS3111R/KE-AS3111W/KE-AS3115W-WM</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_KE_AS3XXX_202602_ES_0854.pdf</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>3018</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KE-DM3110R-KIT</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_KE_DM3110R_KIT_28a2.pdf</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KE-DP3120W/KE-DP3120W-SN/KE-DP3120W-SNV/KE-DP3121W/KE-DP3121W-SN/KE-DP3121W-SNV</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_KE_DP312x_SNx_202503_ES_acf9.pdf</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>4995</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KE-DP3120W/KE-DP3120W-SN/KE-DP3120W-SNV/KE-DP3121B/KE-DP3121B-SNV/KE-DP3121W/KE-DP3121W-SN/KE-DP3121W-SNV</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_KE_DP312x_SNx_202512_ES_242d.pdf</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>KE-IO3144/KE-IU3110</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_KE_IO3144_631e.pdf</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>NC-PF2/NC-PF4/NC-PF8/NC-PF2-SC/NC-PF4-SC/NC-PF8-SC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_NC_PFx_202502_ES_62f8.pdf</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ZLSM-MD</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_ZLSM_MD_202604_ING_1875.pdf</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ZLSM-ME/ZLSM-MR</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_ZLSM_ME_202604_ING_29a1.pdf</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ZLSM-MR</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>MI_KIDDE_ZLSM_MR_202604_ING_252a.pdf</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>N-IO-MBX-1/N-IO-MBX-2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Manual instalación</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>MI_N_IO_MBX_X_202505_ES__1__1fd1.pdf</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2X-AT-FR-FB-S/2X-AT-FR-S</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Manual usuario</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>MU_KIDDE_2X_AT_FR_FB_S_6c31.pdf</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>NC-PF2</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>nc-pf2-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NC-PF4</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>nc-pf4-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NC-PF4-SC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>nc-pf4-sc-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NC-PF8</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>nc-pf8-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>NC-PF8-SC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Datasheet</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>portal</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>nc-pf8-sc-161721-es.pdf</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>617</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>